--- a/Classwork_ML.xlsx
+++ b/Classwork_ML.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1 Corporate Training\Ericsson MS-Excel AI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git Backup\2GITHUB\Secure-Meter-Classwork\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E5FE4AF-1417-48DE-8744-1E4746E2D028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71AC0150-5441-4543-8E3C-DAEACC2E0F07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="823" xr2:uid="{8906883F-2923-499F-A745-AA2DCE968BC0}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="823" firstSheet="3" activeTab="4" xr2:uid="{8906883F-2923-499F-A745-AA2DCE968BC0}"/>
   </bookViews>
   <sheets>
     <sheet name="Forecast Sheet" sheetId="16" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="227">
   <si>
     <t>Day</t>
   </si>
@@ -935,7 +935,7 @@
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1096,8 +1096,15 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1161,6 +1168,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1970,7 +1989,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="312">
+  <cellXfs count="319">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -2520,6 +2539,28 @@
     <xf numFmtId="165" fontId="1" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="12" xfId="2" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2580,29 +2621,18 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="12" xfId="2" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2610,18 +2640,6 @@
     <cellStyle name="Normal 3" xfId="2" xr:uid="{BF4723F8-20E4-4604-9649-A8CA338D86F6}"/>
   </cellStyles>
   <dxfs count="46">
-    <dxf>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="22" formatCode="mmm/yy"/>
-    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -2688,12 +2706,6 @@
           <bgColor theme="9" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="22" formatCode="mmm/yy"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -3277,6 +3289,24 @@
           <color indexed="64"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="22" formatCode="mmm/yy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="22" formatCode="mmm/yy"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -5349,6 +5379,622 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
+              <a:t>Regression Plot</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>x vs. y</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0.44247003499562554"/>
+                  <c:y val="-0.31076407115777194"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Correlation &amp; Regression-1 (2)'!$C$4:$C$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Correlation &amp; Regression-1 (2)'!$D$4:$D$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>82</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>86</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>78</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B035-42D7-80FC-924254A1563B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Test Data</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Correlation &amp; Regression-1 (2)'!$F$14:$F$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>13</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Correlation &amp; Regression-1 (2)'!$G$14:$G$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>66.273631840796014</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>62.651741293532332</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>55.407960199004968</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-B035-42D7-80FC-924254A1563B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="110325632"/>
+        <c:axId val="267866512"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="110325632"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Absence Count</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="267866512"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="267866512"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Final Exam %</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="110325632"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:srgbClr val="C00000"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr b="1"/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
               <a:t>K-NN Classifier</a:t>
             </a:r>
           </a:p>
@@ -6024,7 +6670,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -6690,7 +7336,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -7154,7 +7800,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -7879,7 +8525,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -8566,6 +9212,46 @@
 </file>
 
 <file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors8.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -12167,6 +12853,522 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -12478,6 +13680,42 @@
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>165100</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>469900</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>91440</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1C2A3FF-8472-0AE0-5648-958C8492AD1B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -13301,15 +14539,15 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{32571E9D-90D7-4BBE-A093-A97CAD6B7022}" name="Table10" displayName="Table10" ref="A1:E26" totalsRowShown="0">
   <autoFilter ref="A1:E26" xr:uid="{32571E9D-90D7-4BBE-A093-A97CAD6B7022}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{4DF3B165-221C-4BD9-A096-CC128ECDE1B4}" name="Month" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{4DF3B165-221C-4BD9-A096-CC128ECDE1B4}" name="Month" dataDxfId="45"/>
     <tableColumn id="2" xr3:uid="{DAA7E895-667B-4DCD-9702-F327175EDEEC}" name="Sales"/>
     <tableColumn id="3" xr3:uid="{42826E38-F3DF-478D-8F1D-92EBA2349902}" name="Forecast(Sales)">
       <calculatedColumnFormula>_xlfn.FORECAST.ETS(A2,$B$2:$B$17,$A$2:$A$17,1,1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{4B63942C-AC25-4883-8BF9-7094C285F464}" name="Lower Confidence Bound(Sales)" dataDxfId="2">
+    <tableColumn id="4" xr3:uid="{4B63942C-AC25-4883-8BF9-7094C285F464}" name="Lower Confidence Bound(Sales)" dataDxfId="44">
       <calculatedColumnFormula>C2-_xlfn.FORECAST.ETS.CONFINT(A2,$B$2:$B$17,$A$2:$A$17,0.95,1,1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{62F58AD9-1FC9-46C8-B4E7-2231918EC1E4}" name="Upper Confidence Bound(Sales)" dataDxfId="1">
+    <tableColumn id="5" xr3:uid="{62F58AD9-1FC9-46C8-B4E7-2231918EC1E4}" name="Upper Confidence Bound(Sales)" dataDxfId="43">
       <calculatedColumnFormula>C2+_xlfn.FORECAST.ETS.CONFINT(A2,$B$2:$B$17,$A$2:$A$17,0.95,1,1)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -13322,7 +14560,7 @@
   <autoFilter ref="G1:H8" xr:uid="{686E5E14-5083-4C5A-89B7-749C9412A608}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{3A493A91-0A60-4C4D-BD13-741A12C8B244}" name="Statistic"/>
-    <tableColumn id="2" xr3:uid="{E4BAACB9-6637-4486-ABF6-27B3AE1F8022}" name="Value" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{E4BAACB9-6637-4486-ABF6-27B3AE1F8022}" name="Value" dataDxfId="42"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -13332,7 +14570,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E2171328-598F-4AF9-A570-0C4BF0328BF5}" name="Table4" displayName="Table4" ref="A1:D26" totalsRowShown="0">
   <autoFilter ref="A1:D26" xr:uid="{E2171328-598F-4AF9-A570-0C4BF0328BF5}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{5265A801-7A9B-4D1C-A965-DAFB00FCEA5B}" name="Month" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{5265A801-7A9B-4D1C-A965-DAFB00FCEA5B}" name="Month" dataDxfId="41"/>
     <tableColumn id="2" xr3:uid="{67594A27-DA04-4FA6-B749-64F558278EF3}" name="Sales"/>
     <tableColumn id="3" xr3:uid="{F712BD8F-11A6-422F-8B97-C5F6CC542257}" name="Forecast(Sales)">
       <calculatedColumnFormula>_xlfn.FORECAST.ETS(A2,$B$2:$B$17,$A$2:$A$17,1,1)</calculatedColumnFormula>
@@ -13350,14 +14588,14 @@
   <autoFilter ref="G1:H8" xr:uid="{E2AD9CB9-98BD-4095-8ACC-42C8BFECADCF}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{4207C0C1-6475-41A1-B1AB-5B54F7EB8EC4}" name="Statistic"/>
-    <tableColumn id="2" xr3:uid="{0C3EE6FD-ED66-420C-BF08-9E497CA8F241}" name="Value" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{0C3EE6FD-ED66-420C-BF08-9E497CA8F241}" name="Value" dataDxfId="40"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4AD92B5F-1020-4D03-9587-68CA729E3E46}" name="Table1" displayName="Table1" ref="A1:J151" totalsRowShown="0" tableBorderDxfId="45">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4AD92B5F-1020-4D03-9587-68CA729E3E46}" name="Table1" displayName="Table1" ref="A1:J151" totalsRowShown="0" tableBorderDxfId="39">
   <autoFilter ref="A1:J151" xr:uid="{62B4E930-DFF6-4BF0-9F1C-5E4C67D47D9A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -13374,24 +14612,24 @@
     <sortCondition ref="A2:A151"/>
   </sortState>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{D73B049B-5822-4F37-B26E-760BB10495F5}" name="Serial" dataDxfId="44"/>
-    <tableColumn id="2" xr3:uid="{D910A9B9-D427-48EA-AB9E-200D7BB66C1E}" name="sepal_length" dataDxfId="43"/>
-    <tableColumn id="3" xr3:uid="{039CAD4E-A07E-4F03-9810-EAAE56003B4E}" name="sepal_width" dataDxfId="42"/>
-    <tableColumn id="4" xr3:uid="{312E3EBE-2568-4DC8-AE77-AC20D8199BC2}" name="petal_length" dataDxfId="41"/>
-    <tableColumn id="5" xr3:uid="{3B818CF0-A6EC-4507-82CE-B4C0F12048CA}" name="petal_width" dataDxfId="40"/>
-    <tableColumn id="6" xr3:uid="{9CB5291D-0B1B-49D9-B4D6-537AD2F558ED}" name="species" dataDxfId="39"/>
-    <tableColumn id="7" xr3:uid="{BF7FDB39-9FB3-4F09-A7F3-11EB71B3910A}" name="Euclidean_x000a_Distance" dataDxfId="38">
+    <tableColumn id="1" xr3:uid="{D73B049B-5822-4F37-B26E-760BB10495F5}" name="Serial" dataDxfId="38"/>
+    <tableColumn id="2" xr3:uid="{D910A9B9-D427-48EA-AB9E-200D7BB66C1E}" name="sepal_length" dataDxfId="37"/>
+    <tableColumn id="3" xr3:uid="{039CAD4E-A07E-4F03-9810-EAAE56003B4E}" name="sepal_width" dataDxfId="36"/>
+    <tableColumn id="4" xr3:uid="{312E3EBE-2568-4DC8-AE77-AC20D8199BC2}" name="petal_length" dataDxfId="35"/>
+    <tableColumn id="5" xr3:uid="{3B818CF0-A6EC-4507-82CE-B4C0F12048CA}" name="petal_width" dataDxfId="34"/>
+    <tableColumn id="6" xr3:uid="{9CB5291D-0B1B-49D9-B4D6-537AD2F558ED}" name="species" dataDxfId="33"/>
+    <tableColumn id="7" xr3:uid="{BF7FDB39-9FB3-4F09-A7F3-11EB71B3910A}" name="Euclidean_x000a_Distance" dataDxfId="32">
       <calculatedColumnFormula>SQRT((Table1[[#This Row],[sepal_length]]-$L$4)^2+(Table1[[#This Row],[sepal_width]]-$M$4)^2+(Table1[[#This Row],[petal_length]]-$N$4)^2+(Table1[[#This Row],[petal_width]]-$O$4)^2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{1C636255-9786-4C26-872C-3AE6549828D6}" name="Rank" dataDxfId="37">
+    <tableColumn id="8" xr3:uid="{1C636255-9786-4C26-872C-3AE6549828D6}" name="Rank" dataDxfId="31">
       <calculatedColumnFormula>RANK(Table1[[#This Row],[Euclidean
 Distance]],Table1[Euclidean
 Distance],1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{BA65F439-C13B-4C8C-909A-06FC767773EA}" name="Manhattan_x000a_Distance" dataDxfId="36">
+    <tableColumn id="9" xr3:uid="{BA65F439-C13B-4C8C-909A-06FC767773EA}" name="Manhattan_x000a_Distance" dataDxfId="30">
       <calculatedColumnFormula>ABS(Table1[[#This Row],[sepal_length]]-$L$4)+ABS(Table1[[#This Row],[sepal_width]]-$M$4)+ABS(Table1[[#This Row],[petal_length]]-$N$4)+ABS(Table1[[#This Row],[petal_width]]-$O$4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{F0A0E666-027F-4F02-97C9-425A7307EAAE}" name="Rank2" dataDxfId="35">
+    <tableColumn id="10" xr3:uid="{F0A0E666-027F-4F02-97C9-425A7307EAAE}" name="Rank2" dataDxfId="29">
       <calculatedColumnFormula>RANK(Table1[[#This Row],[Manhattan
 Distance]],Table1[Manhattan
 Distance],1)</calculatedColumnFormula>
@@ -13402,7 +14640,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{03A7292F-1009-4E5F-BA21-AC93ED5FB037}" name="Table14" displayName="Table14" ref="A1:J151" totalsRowShown="0" tableBorderDxfId="34">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{03A7292F-1009-4E5F-BA21-AC93ED5FB037}" name="Table14" displayName="Table14" ref="A1:J151" totalsRowShown="0" tableBorderDxfId="28">
   <autoFilter ref="A1:J151" xr:uid="{62B4E930-DFF6-4BF0-9F1C-5E4C67D47D9A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -13419,31 +14657,31 @@
     <sortCondition ref="A2:A151"/>
   </sortState>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{F6DF16D2-03AA-4E7F-9673-44A0A4C35B1C}" name="Serial" dataDxfId="33"/>
-    <tableColumn id="2" xr3:uid="{A75179BD-7A57-4CAB-8BD0-BC07EBD90770}" name="sepal_length" dataDxfId="32"/>
-    <tableColumn id="3" xr3:uid="{454D6FF2-D615-4F5D-B99E-C0409BA822D1}" name="sepal_width" dataDxfId="31"/>
-    <tableColumn id="4" xr3:uid="{1C52C729-9E7A-4A1E-A720-BA60A2211EE2}" name="petal_length" dataDxfId="30"/>
-    <tableColumn id="5" xr3:uid="{F2420024-0AFA-4949-83BD-9A17B7B9A955}" name="petal_width" dataDxfId="29"/>
-    <tableColumn id="6" xr3:uid="{4D8A186D-14A0-4FA1-BC1E-C6BDE3530FC7}" name="species" dataDxfId="28"/>
-    <tableColumn id="7" xr3:uid="{016AB6AE-A903-4DCC-ACFF-00A7D3E8B0FB}" name="Euclidean_x000a_Distance" dataDxfId="27"/>
-    <tableColumn id="8" xr3:uid="{51B3085D-0C53-4B37-AB90-C08C6402F3ED}" name="Rank" dataDxfId="26"/>
-    <tableColumn id="9" xr3:uid="{CC0342BF-290F-4B65-83F2-36DE7E759A31}" name="Manhattan_x000a_Distance" dataDxfId="25"/>
-    <tableColumn id="10" xr3:uid="{033147C6-EEFE-4D19-8C98-ECC35D33375D}" name="Rank2" dataDxfId="24"/>
+    <tableColumn id="1" xr3:uid="{F6DF16D2-03AA-4E7F-9673-44A0A4C35B1C}" name="Serial" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{A75179BD-7A57-4CAB-8BD0-BC07EBD90770}" name="sepal_length" dataDxfId="26"/>
+    <tableColumn id="3" xr3:uid="{454D6FF2-D615-4F5D-B99E-C0409BA822D1}" name="sepal_width" dataDxfId="25"/>
+    <tableColumn id="4" xr3:uid="{1C52C729-9E7A-4A1E-A720-BA60A2211EE2}" name="petal_length" dataDxfId="24"/>
+    <tableColumn id="5" xr3:uid="{F2420024-0AFA-4949-83BD-9A17B7B9A955}" name="petal_width" dataDxfId="23"/>
+    <tableColumn id="6" xr3:uid="{4D8A186D-14A0-4FA1-BC1E-C6BDE3530FC7}" name="species" dataDxfId="22"/>
+    <tableColumn id="7" xr3:uid="{016AB6AE-A903-4DCC-ACFF-00A7D3E8B0FB}" name="Euclidean_x000a_Distance" dataDxfId="21"/>
+    <tableColumn id="8" xr3:uid="{51B3085D-0C53-4B37-AB90-C08C6402F3ED}" name="Rank" dataDxfId="20"/>
+    <tableColumn id="9" xr3:uid="{CC0342BF-290F-4B65-83F2-36DE7E759A31}" name="Manhattan_x000a_Distance" dataDxfId="19"/>
+    <tableColumn id="10" xr3:uid="{033147C6-EEFE-4D19-8C98-ECC35D33375D}" name="Rank2" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E301F820-565C-459C-9B81-90C3054550D6}" name="Table13" displayName="Table13" ref="M3:S9" headerRowDxfId="23" totalsRowDxfId="20" headerRowBorderDxfId="22" tableBorderDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E301F820-565C-459C-9B81-90C3054550D6}" name="Table13" displayName="Table13" ref="M3:S9" headerRowDxfId="17" totalsRowDxfId="14" headerRowBorderDxfId="16" tableBorderDxfId="15">
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{27E9F5C9-0D3F-46E4-908D-15F1673D4826}" name="Distance" totalsRowLabel="Total" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{972BA92F-997F-4E19-B0CF-4328F9D6CB72}" name="BA" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{53FBB5C6-08DB-4CA1-90AA-CC856F1075E9}" name="FI" dataDxfId="17"/>
-    <tableColumn id="4" xr3:uid="{7C7DEC26-6BB1-45C5-972A-CAE95A8CD19D}" name="MI" dataDxfId="16"/>
-    <tableColumn id="5" xr3:uid="{88E30472-FBE0-46BB-9074-9881AD323715}" name="NA" dataDxfId="15"/>
-    <tableColumn id="6" xr3:uid="{B80765EA-F69C-4A48-9D3A-1BBE1563A6DE}" name="RM" dataDxfId="14"/>
-    <tableColumn id="7" xr3:uid="{BFB6640A-C3E5-427D-8F35-B3D3532CE630}" name="TO" totalsRowFunction="sum" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{27E9F5C9-0D3F-46E4-908D-15F1673D4826}" name="Distance" totalsRowLabel="Total" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{972BA92F-997F-4E19-B0CF-4328F9D6CB72}" name="BA" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{53FBB5C6-08DB-4CA1-90AA-CC856F1075E9}" name="FI" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{7C7DEC26-6BB1-45C5-972A-CAE95A8CD19D}" name="MI" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{88E30472-FBE0-46BB-9074-9881AD323715}" name="NA" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{B80765EA-F69C-4A48-9D3A-1BBE1563A6DE}" name="RM" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{BFB6640A-C3E5-427D-8F35-B3D3532CE630}" name="TO" totalsRowFunction="sum" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="1" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -13754,15 +14992,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="311" t="s">
+      <c r="A1" s="287" t="s">
         <v>207</v>
       </c>
-      <c r="B1" s="311" t="s">
+      <c r="B1" s="287" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="302">
+      <c r="A2" s="282">
         <v>45292</v>
       </c>
       <c r="B2">
@@ -13770,7 +15008,7 @@
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="302">
+      <c r="A3" s="282">
         <v>45323</v>
       </c>
       <c r="B3">
@@ -13778,7 +15016,7 @@
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="302">
+      <c r="A4" s="282">
         <v>45352</v>
       </c>
       <c r="B4">
@@ -13786,7 +15024,7 @@
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="302">
+      <c r="A5" s="282">
         <v>45383</v>
       </c>
       <c r="B5">
@@ -13794,7 +15032,7 @@
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="302">
+      <c r="A6" s="282">
         <v>45413</v>
       </c>
       <c r="B6">
@@ -13802,7 +15040,7 @@
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="302">
+      <c r="A7" s="282">
         <v>45444</v>
       </c>
       <c r="B7">
@@ -13810,7 +15048,7 @@
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="302">
+      <c r="A8" s="282">
         <v>45474</v>
       </c>
       <c r="B8">
@@ -13818,7 +15056,7 @@
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="302">
+      <c r="A9" s="282">
         <v>45505</v>
       </c>
       <c r="B9">
@@ -13826,7 +15064,7 @@
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="302">
+      <c r="A10" s="282">
         <v>45536</v>
       </c>
       <c r="B10">
@@ -13834,7 +15072,7 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="302">
+      <c r="A11" s="282">
         <v>45566</v>
       </c>
       <c r="B11">
@@ -13842,7 +15080,7 @@
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="302">
+      <c r="A12" s="282">
         <v>45597</v>
       </c>
       <c r="B12">
@@ -13850,7 +15088,7 @@
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="302">
+      <c r="A13" s="282">
         <v>45627</v>
       </c>
       <c r="B13">
@@ -13858,7 +15096,7 @@
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="302">
+      <c r="A14" s="282">
         <v>45658</v>
       </c>
       <c r="B14">
@@ -13866,7 +15104,7 @@
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="302">
+      <c r="A15" s="282">
         <v>45689</v>
       </c>
       <c r="B15">
@@ -13874,7 +15112,7 @@
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="302">
+      <c r="A16" s="282">
         <v>45717</v>
       </c>
       <c r="B16">
@@ -13882,7 +15120,7 @@
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="302">
+      <c r="A17" s="282">
         <v>45748</v>
       </c>
       <c r="B17">
@@ -13890,42 +15128,42 @@
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="302">
+      <c r="A18" s="282">
         <v>45778</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="302">
+      <c r="A19" s="282">
         <v>45809</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="302">
+      <c r="A20" s="282">
         <v>45839</v>
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="302">
+      <c r="A21" s="282">
         <v>45870</v>
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="302">
+      <c r="A22" s="282">
         <v>45901</v>
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="302">
+      <c r="A23" s="282">
         <v>45931</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="302">
+      <c r="A24" s="282">
         <v>45962</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="302">
+      <c r="A25" s="282">
         <v>45992</v>
       </c>
     </row>
@@ -13979,11 +15217,11 @@
       <c r="H1" s="39" t="s">
         <v>74</v>
       </c>
-      <c r="J1" s="282" t="s">
+      <c r="J1" s="292" t="s">
         <v>76</v>
       </c>
-      <c r="K1" s="282"/>
-      <c r="L1" s="282"/>
+      <c r="K1" s="292"/>
+      <c r="L1" s="292"/>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="42">
@@ -14378,13 +15616,13 @@
 Distance],1)</f>
         <v>134</v>
       </c>
-      <c r="L2" s="283" t="s">
+      <c r="L2" s="293" t="s">
         <v>76</v>
       </c>
-      <c r="M2" s="283"/>
-      <c r="N2" s="283"/>
-      <c r="O2" s="283"/>
-      <c r="P2" s="283"/>
+      <c r="M2" s="293"/>
+      <c r="N2" s="293"/>
+      <c r="O2" s="293"/>
+      <c r="P2" s="293"/>
     </row>
     <row r="3" spans="1:17" s="179" customFormat="1" ht="13.8" customHeight="1" thickBot="1">
       <c r="A3" s="172">
@@ -20396,16 +21634,16 @@
     <mergeCell ref="L2:P2"/>
   </mergeCells>
   <conditionalFormatting sqref="G2:G151">
-    <cfRule type="top10" dxfId="7" priority="4" bottom="1" rank="5"/>
+    <cfRule type="top10" dxfId="3" priority="4" bottom="1" rank="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H151">
-    <cfRule type="top10" dxfId="6" priority="3" bottom="1" rank="5"/>
+    <cfRule type="top10" dxfId="2" priority="3" bottom="1" rank="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I151">
-    <cfRule type="top10" dxfId="5" priority="2" bottom="1" rank="5"/>
+    <cfRule type="top10" dxfId="1" priority="2" bottom="1" rank="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J151">
-    <cfRule type="top10" dxfId="4" priority="1" bottom="1" rank="5"/>
+    <cfRule type="top10" dxfId="0" priority="1" bottom="1" rank="5"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -20493,13 +21731,13 @@
       <c r="H2" s="84"/>
       <c r="I2" s="85"/>
       <c r="J2" s="82"/>
-      <c r="L2" s="283" t="s">
+      <c r="L2" s="293" t="s">
         <v>76</v>
       </c>
-      <c r="M2" s="283"/>
-      <c r="N2" s="283"/>
-      <c r="O2" s="283"/>
-      <c r="P2" s="283"/>
+      <c r="M2" s="293"/>
+      <c r="N2" s="293"/>
+      <c r="O2" s="293"/>
+      <c r="P2" s="293"/>
     </row>
     <row r="3" spans="1:17" ht="15" thickBot="1">
       <c r="A3" s="86">
@@ -24141,18 +25379,18 @@
   <sheetData>
     <row r="1" spans="2:15" ht="15" thickBot="1"/>
     <row r="2" spans="2:15" ht="15" thickBot="1">
-      <c r="E2" s="284" t="s">
+      <c r="E2" s="294" t="s">
         <v>92</v>
       </c>
-      <c r="F2" s="285"/>
-      <c r="H2" s="284" t="s">
+      <c r="F2" s="295"/>
+      <c r="H2" s="294" t="s">
         <v>92</v>
       </c>
-      <c r="I2" s="285"/>
-      <c r="K2" s="284" t="s">
+      <c r="I2" s="295"/>
+      <c r="K2" s="294" t="s">
         <v>92</v>
       </c>
-      <c r="L2" s="285"/>
+      <c r="L2" s="295"/>
       <c r="O2" s="24" t="s">
         <v>201</v>
       </c>
@@ -24600,10 +25838,10 @@
       </c>
     </row>
     <row r="19" spans="2:6" ht="15" thickBot="1">
-      <c r="B19" s="286" t="s">
+      <c r="B19" s="296" t="s">
         <v>108</v>
       </c>
-      <c r="C19" s="286"/>
+      <c r="C19" s="296"/>
     </row>
     <row r="20" spans="2:6" ht="15" thickBot="1">
       <c r="B20" s="117" t="s">
@@ -24673,18 +25911,18 @@
   <sheetData>
     <row r="1" spans="2:13" ht="15" thickBot="1"/>
     <row r="2" spans="2:13" ht="15" thickBot="1">
-      <c r="E2" s="284" t="s">
+      <c r="E2" s="294" t="s">
         <v>92</v>
       </c>
-      <c r="F2" s="285"/>
-      <c r="H2" s="284" t="s">
+      <c r="F2" s="295"/>
+      <c r="H2" s="294" t="s">
         <v>92</v>
       </c>
-      <c r="I2" s="285"/>
-      <c r="K2" s="284" t="s">
+      <c r="I2" s="295"/>
+      <c r="K2" s="294" t="s">
         <v>92</v>
       </c>
-      <c r="L2" s="285"/>
+      <c r="L2" s="295"/>
     </row>
     <row r="3" spans="2:13" ht="15" thickBot="1">
       <c r="B3" s="104" t="s">
@@ -24911,10 +26149,10 @@
       <c r="D17" s="115"/>
     </row>
     <row r="19" spans="2:6" ht="15" thickBot="1">
-      <c r="B19" s="286" t="s">
+      <c r="B19" s="296" t="s">
         <v>108</v>
       </c>
-      <c r="C19" s="286"/>
+      <c r="C19" s="296"/>
     </row>
     <row r="20" spans="2:6" ht="15" thickBot="1">
       <c r="B20" s="117" t="s">
@@ -24973,19 +26211,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:19" ht="24" thickBot="1">
-      <c r="B1" s="287" t="s">
+      <c r="B1" s="297" t="s">
         <v>112</v>
       </c>
-      <c r="C1" s="288"/>
-      <c r="D1" s="288"/>
-      <c r="E1" s="288"/>
-      <c r="F1" s="288"/>
-      <c r="G1" s="288"/>
-      <c r="H1" s="288"/>
-      <c r="I1" s="288"/>
-      <c r="J1" s="288"/>
-      <c r="K1" s="288"/>
-      <c r="L1" s="289"/>
+      <c r="C1" s="298"/>
+      <c r="D1" s="298"/>
+      <c r="E1" s="298"/>
+      <c r="F1" s="298"/>
+      <c r="G1" s="298"/>
+      <c r="H1" s="298"/>
+      <c r="I1" s="298"/>
+      <c r="J1" s="298"/>
+      <c r="K1" s="298"/>
+      <c r="L1" s="299"/>
     </row>
     <row r="2" spans="2:19" ht="16.2" thickBot="1">
       <c r="B2" s="132"/>
@@ -25630,17 +26868,17 @@
       </c>
     </row>
     <row r="2" spans="2:15" ht="15" thickBot="1">
-      <c r="C2" s="290" t="s">
+      <c r="C2" s="300" t="s">
         <v>130</v>
       </c>
-      <c r="D2" s="291"/>
-      <c r="E2" s="291"/>
-      <c r="F2" s="291"/>
-      <c r="G2" s="291"/>
-      <c r="H2" s="291"/>
-      <c r="I2" s="291"/>
-      <c r="J2" s="291"/>
-      <c r="K2" s="292"/>
+      <c r="D2" s="301"/>
+      <c r="E2" s="301"/>
+      <c r="F2" s="301"/>
+      <c r="G2" s="301"/>
+      <c r="H2" s="301"/>
+      <c r="I2" s="301"/>
+      <c r="J2" s="301"/>
+      <c r="K2" s="302"/>
       <c r="O2" s="1" t="s">
         <v>203</v>
       </c>
@@ -26264,10 +27502,10 @@
       </c>
     </row>
     <row r="17" spans="3:12" ht="15" thickBot="1">
-      <c r="C17" s="293" t="s">
+      <c r="C17" s="303" t="s">
         <v>137</v>
       </c>
-      <c r="D17" s="294"/>
+      <c r="D17" s="304"/>
       <c r="E17" s="205">
         <f>E16-E15</f>
         <v>0.2</v>
@@ -26305,31 +27543,31 @@
       <c r="C18" s="42" t="s">
         <v>133</v>
       </c>
-      <c r="D18" s="295" t="s">
+      <c r="D18" s="305" t="s">
         <v>138</v>
       </c>
-      <c r="E18" s="296"/>
-      <c r="F18" s="296"/>
-      <c r="G18" s="296"/>
-      <c r="H18" s="296"/>
-      <c r="I18" s="296"/>
-      <c r="J18" s="296"/>
-      <c r="K18" s="297"/>
+      <c r="E18" s="306"/>
+      <c r="F18" s="306"/>
+      <c r="G18" s="306"/>
+      <c r="H18" s="306"/>
+      <c r="I18" s="306"/>
+      <c r="J18" s="306"/>
+      <c r="K18" s="307"/>
     </row>
     <row r="19" spans="3:12" ht="15" thickBot="1">
       <c r="C19" s="57" t="s">
         <v>135</v>
       </c>
-      <c r="D19" s="298" t="s">
+      <c r="D19" s="308" t="s">
         <v>139</v>
       </c>
-      <c r="E19" s="299"/>
-      <c r="F19" s="299"/>
-      <c r="G19" s="299"/>
-      <c r="H19" s="299"/>
-      <c r="I19" s="299"/>
-      <c r="J19" s="299"/>
-      <c r="K19" s="300"/>
+      <c r="E19" s="309"/>
+      <c r="F19" s="309"/>
+      <c r="G19" s="309"/>
+      <c r="H19" s="309"/>
+      <c r="I19" s="309"/>
+      <c r="J19" s="309"/>
+      <c r="K19" s="310"/>
     </row>
     <row r="21" spans="3:12">
       <c r="D21" s="1" t="s">
@@ -26614,7 +27852,7 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="302">
+      <c r="A2" s="282">
         <v>45292</v>
       </c>
       <c r="B2">
@@ -26623,13 +27861,13 @@
       <c r="G2" t="s">
         <v>213</v>
       </c>
-      <c r="H2" s="303">
+      <c r="H2" s="283">
         <f>_xlfn.FORECAST.ETS.STAT($B$2:$B$17,$A$2:$A$17,1,1,1)</f>
         <v>0.25</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="302">
+      <c r="A3" s="282">
         <v>45323</v>
       </c>
       <c r="B3">
@@ -26638,13 +27876,13 @@
       <c r="G3" t="s">
         <v>214</v>
       </c>
-      <c r="H3" s="303">
+      <c r="H3" s="283">
         <f>_xlfn.FORECAST.ETS.STAT($B$2:$B$17,$A$2:$A$17,2,1,1)</f>
         <v>1E-3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="302">
+      <c r="A4" s="282">
         <v>45352</v>
       </c>
       <c r="B4">
@@ -26653,13 +27891,13 @@
       <c r="G4" t="s">
         <v>215</v>
       </c>
-      <c r="H4" s="303">
+      <c r="H4" s="283">
         <f>_xlfn.FORECAST.ETS.STAT($B$2:$B$17,$A$2:$A$17,3,1,1)</f>
         <v>2.2204460492503131E-16</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="302">
+      <c r="A5" s="282">
         <v>45383</v>
       </c>
       <c r="B5">
@@ -26668,13 +27906,13 @@
       <c r="G5" t="s">
         <v>216</v>
       </c>
-      <c r="H5" s="303">
+      <c r="H5" s="283">
         <f>_xlfn.FORECAST.ETS.STAT($B$2:$B$17,$A$2:$A$17,4,1,1)</f>
         <v>1.9497085561272305</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="302">
+      <c r="A6" s="282">
         <v>45413</v>
       </c>
       <c r="B6">
@@ -26683,13 +27921,13 @@
       <c r="G6" t="s">
         <v>217</v>
       </c>
-      <c r="H6" s="303">
+      <c r="H6" s="283">
         <f>_xlfn.FORECAST.ETS.STAT($B$2:$B$17,$A$2:$A$17,5,1,1)</f>
         <v>7.9061900774040336E-2</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="302">
+      <c r="A7" s="282">
         <v>45444</v>
       </c>
       <c r="B7">
@@ -26698,13 +27936,13 @@
       <c r="G7" t="s">
         <v>218</v>
       </c>
-      <c r="H7" s="303">
+      <c r="H7" s="283">
         <f>_xlfn.FORECAST.ETS.STAT($B$2:$B$17,$A$2:$A$17,6,1,1)</f>
         <v>133.23008466869408</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="302">
+      <c r="A8" s="282">
         <v>45474</v>
       </c>
       <c r="B8">
@@ -26713,13 +27951,13 @@
       <c r="G8" t="s">
         <v>219</v>
       </c>
-      <c r="H8" s="303">
+      <c r="H8" s="283">
         <f>_xlfn.FORECAST.ETS.STAT($B$2:$B$17,$A$2:$A$17,7,1,1)</f>
         <v>193.65383031527566</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="302">
+      <c r="A9" s="282">
         <v>45505</v>
       </c>
       <c r="B9">
@@ -26727,7 +27965,7 @@
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="302">
+      <c r="A10" s="282">
         <v>45536</v>
       </c>
       <c r="B10">
@@ -26735,7 +27973,7 @@
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="302">
+      <c r="A11" s="282">
         <v>45566</v>
       </c>
       <c r="B11">
@@ -26743,7 +27981,7 @@
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="302">
+      <c r="A12" s="282">
         <v>45597</v>
       </c>
       <c r="B12">
@@ -26751,7 +27989,7 @@
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="302">
+      <c r="A13" s="282">
         <v>45627</v>
       </c>
       <c r="B13">
@@ -26759,7 +27997,7 @@
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="302">
+      <c r="A14" s="282">
         <v>45658</v>
       </c>
       <c r="B14">
@@ -26767,7 +28005,7 @@
       </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="302">
+      <c r="A15" s="282">
         <v>45689</v>
       </c>
       <c r="B15">
@@ -26775,7 +28013,7 @@
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="302">
+      <c r="A16" s="282">
         <v>45717</v>
       </c>
       <c r="B16">
@@ -26783,7 +28021,7 @@
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="302">
+      <c r="A17" s="282">
         <v>45748</v>
       </c>
       <c r="B17">
@@ -26792,163 +28030,163 @@
       <c r="C17">
         <v>1790</v>
       </c>
-      <c r="D17" s="310">
+      <c r="D17" s="286">
         <v>1790</v>
       </c>
-      <c r="E17" s="310">
+      <c r="E17" s="286">
         <v>1790</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="302">
+      <c r="A18" s="282">
         <v>45778</v>
       </c>
       <c r="C18">
-        <f>_xlfn.FORECAST.ETS(A18,$B$2:$B$17,$A$2:$A$17,1,1)</f>
+        <f t="shared" ref="C18:C26" si="0">_xlfn.FORECAST.ETS(A18,$B$2:$B$17,$A$2:$A$17,1,1)</f>
         <v>1776.656176214482</v>
       </c>
-      <c r="D18" s="310">
-        <f>C18-_xlfn.FORECAST.ETS.CONFINT(A18,$B$2:$B$17,$A$2:$A$17,0.95,1,1)</f>
+      <c r="D18" s="286">
+        <f t="shared" ref="D18:D26" si="1">C18-_xlfn.FORECAST.ETS.CONFINT(A18,$B$2:$B$17,$A$2:$A$17,0.95,1,1)</f>
         <v>1472.0054534267915</v>
       </c>
-      <c r="E18" s="310">
-        <f>C18+_xlfn.FORECAST.ETS.CONFINT(A18,$B$2:$B$17,$A$2:$A$17,0.95,1,1)</f>
+      <c r="E18" s="286">
+        <f t="shared" ref="E18:E26" si="2">C18+_xlfn.FORECAST.ETS.CONFINT(A18,$B$2:$B$17,$A$2:$A$17,0.95,1,1)</f>
         <v>2081.3068990021725</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="302">
+      <c r="A19" s="282">
         <v>45809</v>
       </c>
       <c r="C19">
-        <f>_xlfn.FORECAST.ETS(A19,$B$2:$B$17,$A$2:$A$17,1,1)</f>
+        <f t="shared" si="0"/>
         <v>1794.4318639930925</v>
       </c>
-      <c r="D19" s="310">
-        <f>C19-_xlfn.FORECAST.ETS.CONFINT(A19,$B$2:$B$17,$A$2:$A$17,0.95,1,1)</f>
+      <c r="D19" s="286">
+        <f t="shared" si="1"/>
         <v>1480.331059044245</v>
       </c>
-      <c r="E19" s="310">
-        <f>C19+_xlfn.FORECAST.ETS.CONFINT(A19,$B$2:$B$17,$A$2:$A$17,0.95,1,1)</f>
+      <c r="E19" s="286">
+        <f t="shared" si="2"/>
         <v>2108.5326689419398</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="302">
+      <c r="A20" s="282">
         <v>45839</v>
       </c>
       <c r="C20">
-        <f>_xlfn.FORECAST.ETS(A20,$B$2:$B$17,$A$2:$A$17,1,1)</f>
+        <f t="shared" si="0"/>
         <v>1812.2075517717033</v>
       </c>
-      <c r="D20" s="310">
-        <f>C20-_xlfn.FORECAST.ETS.CONFINT(A20,$B$2:$B$17,$A$2:$A$17,0.95,1,1)</f>
+      <c r="D20" s="286">
+        <f t="shared" si="1"/>
         <v>1488.8605973843114</v>
       </c>
-      <c r="E20" s="310">
-        <f>C20+_xlfn.FORECAST.ETS.CONFINT(A20,$B$2:$B$17,$A$2:$A$17,0.95,1,1)</f>
+      <c r="E20" s="286">
+        <f t="shared" si="2"/>
         <v>2135.5545061590951</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="302">
+      <c r="A21" s="282">
         <v>45870</v>
       </c>
       <c r="C21">
-        <f>_xlfn.FORECAST.ETS(A21,$B$2:$B$17,$A$2:$A$17,1,1)</f>
+        <f t="shared" si="0"/>
         <v>1829.9832395503138</v>
       </c>
-      <c r="D21" s="310">
-        <f>C21-_xlfn.FORECAST.ETS.CONFINT(A21,$B$2:$B$17,$A$2:$A$17,0.95,1,1)</f>
+      <c r="D21" s="286">
+        <f t="shared" si="1"/>
         <v>1497.5767711333287</v>
       </c>
-      <c r="E21" s="310">
-        <f>C21+_xlfn.FORECAST.ETS.CONFINT(A21,$B$2:$B$17,$A$2:$A$17,0.95,1,1)</f>
+      <c r="E21" s="286">
+        <f t="shared" si="2"/>
         <v>2162.3897079672988</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="302">
+      <c r="A22" s="282">
         <v>45901</v>
       </c>
       <c r="C22">
-        <f>_xlfn.FORECAST.ETS(A22,$B$2:$B$17,$A$2:$A$17,1,1)</f>
+        <f t="shared" si="0"/>
         <v>1847.7589273289245</v>
       </c>
-      <c r="D22" s="310">
-        <f>C22-_xlfn.FORECAST.ETS.CONFINT(A22,$B$2:$B$17,$A$2:$A$17,0.95,1,1)</f>
+      <c r="D22" s="286">
+        <f t="shared" si="1"/>
         <v>1506.4644455464177</v>
       </c>
-      <c r="E22" s="310">
-        <f>C22+_xlfn.FORECAST.ETS.CONFINT(A22,$B$2:$B$17,$A$2:$A$17,0.95,1,1)</f>
+      <c r="E22" s="286">
+        <f t="shared" si="2"/>
         <v>2189.0534091114314</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="302">
+      <c r="A23" s="282">
         <v>45931</v>
       </c>
       <c r="C23">
-        <f>_xlfn.FORECAST.ETS(A23,$B$2:$B$17,$A$2:$A$17,1,1)</f>
+        <f t="shared" si="0"/>
         <v>1865.5346151075353</v>
       </c>
-      <c r="D23" s="310">
-        <f>C23-_xlfn.FORECAST.ETS.CONFINT(A23,$B$2:$B$17,$A$2:$A$17,0.95,1,1)</f>
+      <c r="D23" s="286">
+        <f t="shared" si="1"/>
         <v>1515.5102906885868</v>
       </c>
-      <c r="E23" s="310">
-        <f>C23+_xlfn.FORECAST.ETS.CONFINT(A23,$B$2:$B$17,$A$2:$A$17,0.95,1,1)</f>
+      <c r="E23" s="286">
+        <f t="shared" si="2"/>
         <v>2215.5589395264838</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="302">
+      <c r="A24" s="282">
         <v>45962</v>
       </c>
       <c r="C24">
-        <f>_xlfn.FORECAST.ETS(A24,$B$2:$B$17,$A$2:$A$17,1,1)</f>
+        <f t="shared" si="0"/>
         <v>1883.3103028861458</v>
       </c>
-      <c r="D24" s="310">
-        <f>C24-_xlfn.FORECAST.ETS.CONFINT(A24,$B$2:$B$17,$A$2:$A$17,0.95,1,1)</f>
+      <c r="D24" s="286">
+        <f t="shared" si="1"/>
         <v>1524.7024961685115</v>
       </c>
-      <c r="E24" s="310">
-        <f>C24+_xlfn.FORECAST.ETS.CONFINT(A24,$B$2:$B$17,$A$2:$A$17,0.95,1,1)</f>
+      <c r="E24" s="286">
+        <f t="shared" si="2"/>
         <v>2241.9181096037801</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="302">
+      <c r="A25" s="282">
         <v>45992</v>
       </c>
       <c r="C25">
-        <f>_xlfn.FORECAST.ETS(A25,$B$2:$B$17,$A$2:$A$17,1,1)</f>
+        <f t="shared" si="0"/>
         <v>1901.0859906647565</v>
       </c>
-      <c r="D25" s="310">
-        <f>C25-_xlfn.FORECAST.ETS.CONFINT(A25,$B$2:$B$17,$A$2:$A$17,0.95,1,1)</f>
+      <c r="D25" s="286">
+        <f t="shared" si="1"/>
         <v>1534.0305412010712</v>
       </c>
-      <c r="E25" s="310">
-        <f>C25+_xlfn.FORECAST.ETS.CONFINT(A25,$B$2:$B$17,$A$2:$A$17,0.95,1,1)</f>
+      <c r="E25" s="286">
+        <f t="shared" si="2"/>
         <v>2268.1414401284419</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="302">
+      <c r="A26" s="282">
         <v>46022</v>
       </c>
       <c r="C26">
-        <f>_xlfn.FORECAST.ETS(A26,$B$2:$B$17,$A$2:$A$17,1,1)</f>
+        <f t="shared" si="0"/>
         <v>1918.288269160186</v>
       </c>
-      <c r="D26" s="310">
-        <f>C26-_xlfn.FORECAST.ETS.CONFINT(A26,$B$2:$B$17,$A$2:$A$17,0.95,1,1)</f>
+      <c r="D26" s="286">
+        <f t="shared" si="1"/>
         <v>1543.1771433868537</v>
       </c>
-      <c r="E26" s="310">
-        <f>C26+_xlfn.FORECAST.ETS.CONFINT(A26,$B$2:$B$17,$A$2:$A$17,0.95,1,1)</f>
+      <c r="E26" s="286">
+        <f t="shared" si="2"/>
         <v>2293.3993949335181</v>
       </c>
     </row>
@@ -26994,7 +28232,7 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="302">
+      <c r="A2" s="282">
         <v>45292</v>
       </c>
       <c r="B2">
@@ -27003,13 +28241,13 @@
       <c r="G2" t="s">
         <v>213</v>
       </c>
-      <c r="H2" s="303">
+      <c r="H2" s="283">
         <f>_xlfn.FORECAST.ETS.STAT($B$2:$B$17,$A$2:$A$17,1,1,1)</f>
         <v>0.25</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="302">
+      <c r="A3" s="282">
         <v>45323</v>
       </c>
       <c r="B3">
@@ -27018,13 +28256,13 @@
       <c r="G3" t="s">
         <v>214</v>
       </c>
-      <c r="H3" s="303">
+      <c r="H3" s="283">
         <f>_xlfn.FORECAST.ETS.STAT($B$2:$B$17,$A$2:$A$17,2,1,1)</f>
         <v>1E-3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="302">
+      <c r="A4" s="282">
         <v>45352</v>
       </c>
       <c r="B4">
@@ -27033,13 +28271,13 @@
       <c r="G4" t="s">
         <v>215</v>
       </c>
-      <c r="H4" s="303">
+      <c r="H4" s="283">
         <f>_xlfn.FORECAST.ETS.STAT($B$2:$B$17,$A$2:$A$17,3,1,1)</f>
         <v>2.2204460492503131E-16</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="302">
+      <c r="A5" s="282">
         <v>45383</v>
       </c>
       <c r="B5">
@@ -27048,13 +28286,13 @@
       <c r="G5" t="s">
         <v>216</v>
       </c>
-      <c r="H5" s="303">
+      <c r="H5" s="283">
         <f>_xlfn.FORECAST.ETS.STAT($B$2:$B$17,$A$2:$A$17,4,1,1)</f>
         <v>1.9497085561272305</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="302">
+      <c r="A6" s="282">
         <v>45413</v>
       </c>
       <c r="B6">
@@ -27063,13 +28301,13 @@
       <c r="G6" t="s">
         <v>217</v>
       </c>
-      <c r="H6" s="303">
+      <c r="H6" s="283">
         <f>_xlfn.FORECAST.ETS.STAT($B$2:$B$17,$A$2:$A$17,5,1,1)</f>
         <v>7.9061900774040336E-2</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="302">
+      <c r="A7" s="282">
         <v>45444</v>
       </c>
       <c r="B7">
@@ -27078,13 +28316,13 @@
       <c r="G7" t="s">
         <v>218</v>
       </c>
-      <c r="H7" s="303">
+      <c r="H7" s="283">
         <f>_xlfn.FORECAST.ETS.STAT($B$2:$B$17,$A$2:$A$17,6,1,1)</f>
         <v>133.23008466869408</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="302">
+      <c r="A8" s="282">
         <v>45474</v>
       </c>
       <c r="B8">
@@ -27093,13 +28331,13 @@
       <c r="G8" t="s">
         <v>219</v>
       </c>
-      <c r="H8" s="303">
+      <c r="H8" s="283">
         <f>_xlfn.FORECAST.ETS.STAT($B$2:$B$17,$A$2:$A$17,7,1,1)</f>
         <v>193.65383031527566</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="302">
+      <c r="A9" s="282">
         <v>45505</v>
       </c>
       <c r="B9">
@@ -27107,7 +28345,7 @@
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="302">
+      <c r="A10" s="282">
         <v>45536</v>
       </c>
       <c r="B10">
@@ -27115,7 +28353,7 @@
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="302">
+      <c r="A11" s="282">
         <v>45566</v>
       </c>
       <c r="B11">
@@ -27123,7 +28361,7 @@
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="302">
+      <c r="A12" s="282">
         <v>45597</v>
       </c>
       <c r="B12">
@@ -27131,7 +28369,7 @@
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="302">
+      <c r="A13" s="282">
         <v>45627</v>
       </c>
       <c r="B13">
@@ -27139,7 +28377,7 @@
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="302">
+      <c r="A14" s="282">
         <v>45658</v>
       </c>
       <c r="B14">
@@ -27147,7 +28385,7 @@
       </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="302">
+      <c r="A15" s="282">
         <v>45689</v>
       </c>
       <c r="B15">
@@ -27155,7 +28393,7 @@
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="302">
+      <c r="A16" s="282">
         <v>45717</v>
       </c>
       <c r="B16">
@@ -27163,7 +28401,7 @@
       </c>
     </row>
     <row r="17" spans="1:15">
-      <c r="A17" s="302">
+      <c r="A17" s="282">
         <v>45748</v>
       </c>
       <c r="B17">
@@ -27171,240 +28409,228 @@
       </c>
     </row>
     <row r="18" spans="1:15">
-      <c r="A18" s="302">
+      <c r="A18" s="282">
         <v>45778</v>
       </c>
       <c r="C18">
-        <f>_xlfn.FORECAST.ETS(A18,$B$2:$B$17,$A$2:$A$17,1,1)</f>
+        <f t="shared" ref="C18:C26" si="0">_xlfn.FORECAST.ETS(A18,$B$2:$B$17,$A$2:$A$17,1,1)</f>
         <v>1776.656176214482</v>
       </c>
       <c r="D18">
-        <f>_xlfn.FORECAST.ETS.CONFINT(A18,$B$2:$B$17,$A$2:$A$17,0.95,1,1)</f>
+        <f t="shared" ref="D18:D26" si="1">_xlfn.FORECAST.ETS.CONFINT(A18,$B$2:$B$17,$A$2:$A$17,0.95,1,1)</f>
         <v>304.65072278769037</v>
       </c>
     </row>
     <row r="19" spans="1:15">
-      <c r="A19" s="302">
+      <c r="A19" s="282">
         <v>45809</v>
       </c>
       <c r="C19">
-        <f>_xlfn.FORECAST.ETS(A19,$B$2:$B$17,$A$2:$A$17,1,1)</f>
+        <f t="shared" si="0"/>
         <v>1794.4318639930925</v>
       </c>
       <c r="D19">
-        <f>_xlfn.FORECAST.ETS.CONFINT(A19,$B$2:$B$17,$A$2:$A$17,0.95,1,1)</f>
+        <f t="shared" si="1"/>
         <v>314.1008049488475</v>
       </c>
     </row>
     <row r="20" spans="1:15">
-      <c r="A20" s="302">
+      <c r="A20" s="282">
         <v>45839</v>
       </c>
       <c r="C20">
-        <f>_xlfn.FORECAST.ETS(A20,$B$2:$B$17,$A$2:$A$17,1,1)</f>
+        <f t="shared" si="0"/>
         <v>1812.2075517717033</v>
       </c>
       <c r="D20">
-        <f>_xlfn.FORECAST.ETS.CONFINT(A20,$B$2:$B$17,$A$2:$A$17,0.95,1,1)</f>
+        <f t="shared" si="1"/>
         <v>323.34695438739175</v>
       </c>
     </row>
     <row r="21" spans="1:15">
-      <c r="A21" s="302">
+      <c r="A21" s="282">
         <v>45870</v>
       </c>
       <c r="C21">
-        <f>_xlfn.FORECAST.ETS(A21,$B$2:$B$17,$A$2:$A$17,1,1)</f>
+        <f t="shared" si="0"/>
         <v>1829.9832395503138</v>
       </c>
       <c r="D21">
-        <f>_xlfn.FORECAST.ETS.CONFINT(A21,$B$2:$B$17,$A$2:$A$17,0.95,1,1)</f>
+        <f t="shared" si="1"/>
         <v>332.40646841698498</v>
       </c>
     </row>
     <row r="22" spans="1:15">
-      <c r="A22" s="302">
+      <c r="A22" s="282">
         <v>45901</v>
       </c>
       <c r="C22">
-        <f>_xlfn.FORECAST.ETS(A22,$B$2:$B$17,$A$2:$A$17,1,1)</f>
+        <f t="shared" si="0"/>
         <v>1847.7589273289245</v>
       </c>
       <c r="D22">
-        <f>_xlfn.FORECAST.ETS.CONFINT(A22,$B$2:$B$17,$A$2:$A$17,0.95,1,1)</f>
+        <f t="shared" si="1"/>
         <v>341.29448178250681</v>
       </c>
     </row>
     <row r="23" spans="1:15">
-      <c r="A23" s="302">
+      <c r="A23" s="282">
         <v>45931</v>
       </c>
       <c r="C23">
-        <f>_xlfn.FORECAST.ETS(A23,$B$2:$B$17,$A$2:$A$17,1,1)</f>
+        <f t="shared" si="0"/>
         <v>1865.5346151075353</v>
       </c>
       <c r="D23">
-        <f>_xlfn.FORECAST.ETS.CONFINT(A23,$B$2:$B$17,$A$2:$A$17,0.95,1,1)</f>
+        <f t="shared" si="1"/>
         <v>350.02432441894848</v>
       </c>
     </row>
     <row r="24" spans="1:15">
-      <c r="A24" s="302">
+      <c r="A24" s="282">
         <v>45962</v>
       </c>
       <c r="C24">
-        <f>_xlfn.FORECAST.ETS(A24,$B$2:$B$17,$A$2:$A$17,1,1)</f>
+        <f t="shared" si="0"/>
         <v>1883.3103028861458</v>
       </c>
       <c r="D24">
-        <f>_xlfn.FORECAST.ETS.CONFINT(A24,$B$2:$B$17,$A$2:$A$17,0.95,1,1)</f>
+        <f t="shared" si="1"/>
         <v>358.60780671763422</v>
       </c>
     </row>
     <row r="25" spans="1:15">
-      <c r="A25" s="302">
+      <c r="A25" s="282">
         <v>45992</v>
       </c>
       <c r="C25">
-        <f>_xlfn.FORECAST.ETS(A25,$B$2:$B$17,$A$2:$A$17,1,1)</f>
+        <f t="shared" si="0"/>
         <v>1901.0859906647565</v>
       </c>
       <c r="D25">
-        <f>_xlfn.FORECAST.ETS.CONFINT(A25,$B$2:$B$17,$A$2:$A$17,0.95,1,1)</f>
+        <f t="shared" si="1"/>
         <v>367.05544946368531</v>
       </c>
     </row>
     <row r="26" spans="1:15">
-      <c r="A26" s="302">
+      <c r="A26" s="282">
         <v>46022</v>
       </c>
       <c r="C26">
-        <f>_xlfn.FORECAST.ETS(A26,$B$2:$B$17,$A$2:$A$17,1,1)</f>
+        <f t="shared" si="0"/>
         <v>1918.288269160186</v>
       </c>
       <c r="D26">
-        <f>_xlfn.FORECAST.ETS.CONFINT(A26,$B$2:$B$17,$A$2:$A$17,0.95,1,1)</f>
+        <f t="shared" si="1"/>
         <v>375.11112577333228</v>
       </c>
     </row>
     <row r="30" spans="1:15" ht="14.4" customHeight="1">
-      <c r="B30" s="306" t="s">
+      <c r="B30" s="288" t="s">
         <v>220</v>
       </c>
-      <c r="C30" s="306"/>
-      <c r="D30" s="306"/>
-      <c r="E30" s="306"/>
-      <c r="F30" s="306"/>
-      <c r="G30" s="306"/>
-      <c r="H30" s="306"/>
-      <c r="I30" s="306"/>
-      <c r="J30" s="306"/>
-      <c r="K30" s="306"/>
-      <c r="L30" s="306"/>
-      <c r="M30" s="307"/>
-      <c r="N30" s="307"/>
-      <c r="O30" s="307"/>
+      <c r="C30" s="288"/>
+      <c r="D30" s="288"/>
+      <c r="E30" s="288"/>
+      <c r="F30" s="288"/>
+      <c r="G30" s="288"/>
+      <c r="H30" s="288"/>
+      <c r="I30" s="288"/>
+      <c r="J30" s="288"/>
+      <c r="K30" s="288"/>
+      <c r="L30" s="288"/>
+      <c r="M30" s="285"/>
+      <c r="N30" s="285"/>
+      <c r="O30" s="285"/>
     </row>
     <row r="31" spans="1:15">
-      <c r="B31" s="306"/>
-      <c r="C31" s="306"/>
-      <c r="D31" s="306"/>
-      <c r="E31" s="306"/>
-      <c r="F31" s="306"/>
-      <c r="G31" s="306"/>
-      <c r="H31" s="306"/>
-      <c r="I31" s="306"/>
-      <c r="J31" s="306"/>
-      <c r="K31" s="306"/>
-      <c r="L31" s="306"/>
-      <c r="M31" s="307"/>
-      <c r="N31" s="307"/>
-      <c r="O31" s="307"/>
+      <c r="B31" s="288"/>
+      <c r="C31" s="288"/>
+      <c r="D31" s="288"/>
+      <c r="E31" s="288"/>
+      <c r="F31" s="288"/>
+      <c r="G31" s="288"/>
+      <c r="H31" s="288"/>
+      <c r="I31" s="288"/>
+      <c r="J31" s="288"/>
+      <c r="K31" s="288"/>
+      <c r="L31" s="288"/>
+      <c r="M31" s="285"/>
+      <c r="N31" s="285"/>
+      <c r="O31" s="285"/>
     </row>
     <row r="33" spans="2:12" ht="18">
-      <c r="B33" s="304" t="s">
+      <c r="B33" s="284" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="34" spans="2:12">
-      <c r="B34" s="308" t="s">
+      <c r="B34" s="290" t="s">
         <v>222</v>
       </c>
-      <c r="C34" s="308"/>
-      <c r="D34" s="308"/>
-      <c r="E34" s="308"/>
-      <c r="F34" s="308"/>
-      <c r="G34" s="308"/>
-      <c r="H34" s="308"/>
-      <c r="I34" s="308"/>
-      <c r="J34" s="308"/>
-      <c r="K34" s="308"/>
-    </row>
-    <row r="35" spans="2:12">
-      <c r="C35" s="305"/>
-      <c r="D35" s="305"/>
-      <c r="E35" s="305"/>
-      <c r="F35" s="305"/>
-      <c r="G35" s="305"/>
-      <c r="H35" s="305"/>
-      <c r="I35" s="305"/>
-      <c r="J35" s="305"/>
-      <c r="K35" s="305"/>
-      <c r="L35" s="305"/>
+      <c r="C34" s="290"/>
+      <c r="D34" s="290"/>
+      <c r="E34" s="290"/>
+      <c r="F34" s="290"/>
+      <c r="G34" s="290"/>
+      <c r="H34" s="290"/>
+      <c r="I34" s="290"/>
+      <c r="J34" s="290"/>
+      <c r="K34" s="290"/>
     </row>
     <row r="36" spans="2:12">
-      <c r="B36" s="309" t="s">
+      <c r="B36" s="289" t="s">
         <v>223</v>
       </c>
-      <c r="C36" s="309"/>
-      <c r="D36" s="309"/>
-      <c r="E36" s="309"/>
-      <c r="F36" s="309"/>
-      <c r="G36" s="309"/>
-      <c r="H36" s="309"/>
-      <c r="I36" s="309"/>
-      <c r="J36" s="309"/>
-      <c r="K36" s="309"/>
-      <c r="L36" s="309"/>
+      <c r="C36" s="289"/>
+      <c r="D36" s="289"/>
+      <c r="E36" s="289"/>
+      <c r="F36" s="289"/>
+      <c r="G36" s="289"/>
+      <c r="H36" s="289"/>
+      <c r="I36" s="289"/>
+      <c r="J36" s="289"/>
+      <c r="K36" s="289"/>
+      <c r="L36" s="289"/>
     </row>
     <row r="37" spans="2:12">
-      <c r="B37" s="309"/>
-      <c r="C37" s="309"/>
-      <c r="D37" s="309"/>
-      <c r="E37" s="309"/>
-      <c r="F37" s="309"/>
-      <c r="G37" s="309"/>
-      <c r="H37" s="309"/>
-      <c r="I37" s="309"/>
-      <c r="J37" s="309"/>
-      <c r="K37" s="309"/>
-      <c r="L37" s="309"/>
+      <c r="B37" s="289"/>
+      <c r="C37" s="289"/>
+      <c r="D37" s="289"/>
+      <c r="E37" s="289"/>
+      <c r="F37" s="289"/>
+      <c r="G37" s="289"/>
+      <c r="H37" s="289"/>
+      <c r="I37" s="289"/>
+      <c r="J37" s="289"/>
+      <c r="K37" s="289"/>
+      <c r="L37" s="289"/>
     </row>
     <row r="39" spans="2:12">
-      <c r="B39" s="309" t="s">
+      <c r="B39" s="289" t="s">
         <v>224</v>
       </c>
-      <c r="C39" s="309"/>
-      <c r="D39" s="309"/>
-      <c r="E39" s="309"/>
-      <c r="F39" s="309"/>
-      <c r="G39" s="309"/>
-      <c r="H39" s="309"/>
-      <c r="I39" s="309"/>
-      <c r="J39" s="309"/>
-      <c r="K39" s="309"/>
+      <c r="C39" s="289"/>
+      <c r="D39" s="289"/>
+      <c r="E39" s="289"/>
+      <c r="F39" s="289"/>
+      <c r="G39" s="289"/>
+      <c r="H39" s="289"/>
+      <c r="I39" s="289"/>
+      <c r="J39" s="289"/>
+      <c r="K39" s="289"/>
     </row>
     <row r="40" spans="2:12">
-      <c r="B40" s="309"/>
-      <c r="C40" s="309"/>
-      <c r="D40" s="309"/>
-      <c r="E40" s="309"/>
-      <c r="F40" s="309"/>
-      <c r="G40" s="309"/>
-      <c r="H40" s="309"/>
-      <c r="I40" s="309"/>
-      <c r="J40" s="309"/>
-      <c r="K40" s="309"/>
+      <c r="B40" s="289"/>
+      <c r="C40" s="289"/>
+      <c r="D40" s="289"/>
+      <c r="E40" s="289"/>
+      <c r="F40" s="289"/>
+      <c r="G40" s="289"/>
+      <c r="H40" s="289"/>
+      <c r="I40" s="289"/>
+      <c r="J40" s="289"/>
+      <c r="K40" s="289"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -27672,7 +28898,7 @@
         <f>$C$17+$C$18*F14</f>
         <v>77.139303482587067</v>
       </c>
-      <c r="H14" s="301">
+      <c r="H14" s="281">
         <f>_xlfn.FORECAST.LINEAR(F14,$D$4:$D$10,$C$4:$C$10)</f>
         <v>77.139303482587053</v>
       </c>
@@ -27695,7 +28921,7 @@
         <f t="shared" ref="G15:G16" si="3">$C$17+$C$18*F15</f>
         <v>66.273631840796014</v>
       </c>
-      <c r="H15" s="301">
+      <c r="H15" s="281">
         <f t="shared" ref="H15:H16" si="4">_xlfn.FORECAST.LINEAR(F15,$D$4:$D$10,$C$4:$C$10)</f>
         <v>66.273631840796014</v>
       </c>
@@ -27718,7 +28944,7 @@
         <f t="shared" si="3"/>
         <v>62.651741293532339</v>
       </c>
-      <c r="H16" s="301">
+      <c r="H16" s="281">
         <f t="shared" si="4"/>
         <v>62.651741293532332</v>
       </c>
@@ -27824,9 +29050,18 @@
       <c r="D4" s="244">
         <v>82</v>
       </c>
-      <c r="E4" s="245"/>
-      <c r="F4" s="245"/>
-      <c r="G4" s="245"/>
+      <c r="E4" s="245">
+        <f>C4*D4</f>
+        <v>492</v>
+      </c>
+      <c r="F4" s="245">
+        <f>C4^2</f>
+        <v>36</v>
+      </c>
+      <c r="G4" s="245">
+        <f>D4^2</f>
+        <v>6724</v>
+      </c>
     </row>
     <row r="5" spans="1:7">
       <c r="B5" s="244" t="s">
@@ -27838,9 +29073,18 @@
       <c r="D5" s="244">
         <v>86</v>
       </c>
-      <c r="E5" s="245"/>
-      <c r="F5" s="245"/>
-      <c r="G5" s="245"/>
+      <c r="E5" s="245">
+        <f t="shared" ref="E5:E10" si="0">C5*D5</f>
+        <v>172</v>
+      </c>
+      <c r="F5" s="245">
+        <f t="shared" ref="F5:F10" si="1">C5^2</f>
+        <v>4</v>
+      </c>
+      <c r="G5" s="245">
+        <f t="shared" ref="G5:G10" si="2">D5^2</f>
+        <v>7396</v>
+      </c>
     </row>
     <row r="6" spans="1:7">
       <c r="B6" s="244" t="s">
@@ -27852,9 +29096,18 @@
       <c r="D6" s="244">
         <v>43</v>
       </c>
-      <c r="E6" s="245"/>
-      <c r="F6" s="245"/>
-      <c r="G6" s="245"/>
+      <c r="E6" s="245">
+        <f t="shared" si="0"/>
+        <v>645</v>
+      </c>
+      <c r="F6" s="245">
+        <f t="shared" si="1"/>
+        <v>225</v>
+      </c>
+      <c r="G6" s="245">
+        <f t="shared" si="2"/>
+        <v>1849</v>
+      </c>
     </row>
     <row r="7" spans="1:7">
       <c r="B7" s="244" t="s">
@@ -27866,9 +29119,18 @@
       <c r="D7" s="244">
         <v>74</v>
       </c>
-      <c r="E7" s="245"/>
-      <c r="F7" s="245"/>
-      <c r="G7" s="245"/>
+      <c r="E7" s="245">
+        <f t="shared" si="0"/>
+        <v>666</v>
+      </c>
+      <c r="F7" s="245">
+        <f t="shared" si="1"/>
+        <v>81</v>
+      </c>
+      <c r="G7" s="245">
+        <f t="shared" si="2"/>
+        <v>5476</v>
+      </c>
     </row>
     <row r="8" spans="1:7">
       <c r="B8" s="244" t="s">
@@ -27880,9 +29142,18 @@
       <c r="D8" s="244">
         <v>58</v>
       </c>
-      <c r="E8" s="245"/>
-      <c r="F8" s="245"/>
-      <c r="G8" s="245"/>
+      <c r="E8" s="245">
+        <f t="shared" si="0"/>
+        <v>696</v>
+      </c>
+      <c r="F8" s="245">
+        <f t="shared" si="1"/>
+        <v>144</v>
+      </c>
+      <c r="G8" s="245">
+        <f t="shared" si="2"/>
+        <v>3364</v>
+      </c>
     </row>
     <row r="9" spans="1:7">
       <c r="B9" s="244" t="s">
@@ -27894,9 +29165,18 @@
       <c r="D9" s="244">
         <v>90</v>
       </c>
-      <c r="E9" s="245"/>
-      <c r="F9" s="245"/>
-      <c r="G9" s="245"/>
+      <c r="E9" s="245">
+        <f t="shared" si="0"/>
+        <v>450</v>
+      </c>
+      <c r="F9" s="245">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="G9" s="245">
+        <f t="shared" si="2"/>
+        <v>8100</v>
+      </c>
     </row>
     <row r="10" spans="1:7">
       <c r="B10" s="244" t="s">
@@ -27908,14 +29188,49 @@
       <c r="D10" s="244">
         <v>78</v>
       </c>
-      <c r="E10" s="245"/>
-      <c r="F10" s="245"/>
-      <c r="G10" s="245"/>
+      <c r="E10" s="245">
+        <f t="shared" si="0"/>
+        <v>624</v>
+      </c>
+      <c r="F10" s="245">
+        <f t="shared" si="1"/>
+        <v>64</v>
+      </c>
+      <c r="G10" s="245">
+        <f t="shared" si="2"/>
+        <v>6084</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="C11" s="56">
+        <f t="shared" ref="C11:G11" si="3">SUM(C4:C10)</f>
+        <v>57</v>
+      </c>
+      <c r="D11" s="56">
+        <f t="shared" si="3"/>
+        <v>511</v>
+      </c>
+      <c r="E11" s="56">
+        <f t="shared" si="3"/>
+        <v>3745</v>
+      </c>
+      <c r="F11" s="56">
+        <f t="shared" si="3"/>
+        <v>579</v>
+      </c>
+      <c r="G11" s="56">
+        <f t="shared" si="3"/>
+        <v>38993</v>
+      </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="246" t="s">
         <v>188</v>
       </c>
+      <c r="B13" s="56">
+        <f>COUNTA(B4:B10)</f>
+        <v>7</v>
+      </c>
       <c r="E13" s="243" t="s">
         <v>151</v>
       </c>
@@ -27930,42 +29245,67 @@
       <c r="A14" s="246" t="s">
         <v>189</v>
       </c>
+      <c r="B14" s="56">
+        <f>(B13*E11-C11*D11)/SQRT((B13*F11-C11^2)*(B13*G11-D11^2))</f>
+        <v>-0.94421517068791783</v>
+      </c>
       <c r="E14" s="244" t="s">
         <v>190</v>
       </c>
       <c r="F14" s="244">
         <v>10</v>
       </c>
-      <c r="G14" s="245"/>
+      <c r="G14" s="245">
+        <f>$B$19+$B$20*F14</f>
+        <v>66.273631840796014</v>
+      </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="246" t="s">
         <v>189</v>
       </c>
+      <c r="B15" s="56">
+        <f>CORREL(C4:C10,D4:D10)</f>
+        <v>-0.94421517068791805</v>
+      </c>
       <c r="E15" s="244" t="s">
         <v>191</v>
       </c>
       <c r="F15" s="244">
         <v>11</v>
       </c>
-      <c r="G15" s="245"/>
+      <c r="G15" s="245">
+        <f t="shared" ref="G15:G16" si="4">$B$19+$B$20*F15</f>
+        <v>62.651741293532332</v>
+      </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="246" t="s">
         <v>189</v>
       </c>
+      <c r="B16" s="56">
+        <f>CORREL(D4:D10,C4:C10)</f>
+        <v>-0.94421517068791805</v>
+      </c>
       <c r="E16" s="244" t="s">
         <v>192</v>
       </c>
       <c r="F16" s="244">
         <v>13</v>
       </c>
-      <c r="G16" s="245"/>
+      <c r="G16" s="245">
+        <f t="shared" si="4"/>
+        <v>55.407960199004968</v>
+      </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="246" t="s">
         <v>193</v>
       </c>
+      <c r="B17" s="56">
+        <f>(D11*F11-C11*E11)/(B13*F11-C11^2)</f>
+        <v>102.49253731343283</v>
+      </c>
       <c r="C17" s="56" t="s">
         <v>194</v>
       </c>
@@ -27974,6 +29314,10 @@
       <c r="A18" s="246" t="s">
         <v>195</v>
       </c>
+      <c r="B18" s="56">
+        <f>(B13*E11-C11*D11)/(B13*F11-C11^2)</f>
+        <v>-3.6218905472636815</v>
+      </c>
       <c r="C18" s="56" t="s">
         <v>196</v>
       </c>
@@ -27982,6 +29326,10 @@
       <c r="A19" s="246" t="s">
         <v>193</v>
       </c>
+      <c r="B19" s="56">
+        <f>INTERCEPT(D4:D10,C4:C10)</f>
+        <v>102.49253731343283</v>
+      </c>
       <c r="C19" s="56" t="s">
         <v>194</v>
       </c>
@@ -27990,6 +29338,10 @@
       <c r="A20" s="246" t="s">
         <v>195</v>
       </c>
+      <c r="B20" s="56">
+        <f>SLOPE(D4:D10,C4:C10)</f>
+        <v>-3.621890547263682</v>
+      </c>
       <c r="C20" s="56" t="s">
         <v>196</v>
       </c>
@@ -27998,9 +29350,13 @@
       <c r="A21" s="246" t="s">
         <v>197</v>
       </c>
+      <c r="B21" s="56">
+        <f>B14^2</f>
+        <v>0.89154228855721385</v>
+      </c>
       <c r="C21" s="247">
         <f>B21</f>
-        <v>0</v>
+        <v>0.89154228855721385</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -28460,14 +29816,31 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51438EFF-E703-441C-97DD-F68840B6F847}">
-  <dimension ref="B1:G12"/>
+  <dimension ref="B1:Q23"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="16384" width="8.88671875" style="56"/>
+    <col min="1" max="1" width="8.88671875" style="56"/>
+    <col min="2" max="2" width="7.21875" style="56" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4" style="56" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.6640625" style="56" customWidth="1"/>
+    <col min="5" max="5" width="4" style="56" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.44140625" style="56" customWidth="1"/>
+    <col min="7" max="7" width="7.6640625" style="56" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.88671875" style="56"/>
+    <col min="9" max="9" width="16.77734375" style="56" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.88671875" style="56" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.44140625" style="56" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.88671875" style="56" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.21875" style="56" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.21875" style="56" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.21875" style="56" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.88671875" style="56" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.44140625" style="56" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="8.88671875" style="56"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="14.4" thickBot="1"/>
-    <row r="2" spans="2:7" ht="14.4" thickBot="1">
+    <row r="1" spans="2:17" ht="14.4" thickBot="1"/>
+    <row r="2" spans="2:17" ht="15" thickBot="1">
       <c r="B2" s="222" t="s">
         <v>151</v>
       </c>
@@ -28486,8 +29859,19 @@
       <c r="G2" s="222" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="3" spans="2:7">
+      <c r="I2" t="s">
+        <v>157</v>
+      </c>
+      <c r="J2"/>
+      <c r="K2"/>
+      <c r="L2"/>
+      <c r="M2"/>
+      <c r="N2"/>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+    </row>
+    <row r="3" spans="2:17" ht="15" thickBot="1">
       <c r="B3" s="225" t="s">
         <v>51</v>
       </c>
@@ -28500,10 +29884,25 @@
       <c r="E3" s="227">
         <v>550</v>
       </c>
-      <c r="F3" s="227"/>
-      <c r="G3" s="227"/>
-    </row>
-    <row r="4" spans="2:7">
+      <c r="F3" s="227">
+        <f>$J$18+$J$19*C3+$J$20*D3</f>
+        <v>555.36373267414149</v>
+      </c>
+      <c r="G3" s="227">
+        <f>(E3-F3)^2</f>
+        <v>28.769628199652999</v>
+      </c>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
+      <c r="N3"/>
+      <c r="O3"/>
+      <c r="P3"/>
+      <c r="Q3"/>
+    </row>
+    <row r="4" spans="2:17" ht="14.4">
       <c r="B4" s="228" t="s">
         <v>55</v>
       </c>
@@ -28516,10 +29915,27 @@
       <c r="E4" s="230">
         <v>570</v>
       </c>
-      <c r="F4" s="230"/>
-      <c r="G4" s="230"/>
-    </row>
-    <row r="5" spans="2:7">
+      <c r="F4" s="227">
+        <f t="shared" ref="F4:F7" si="0">$J$18+$J$19*C4+$J$20*D4</f>
+        <v>584.20852829522391</v>
+      </c>
+      <c r="G4" s="227">
+        <f t="shared" ref="G4:G7" si="1">(E4-F4)^2</f>
+        <v>201.88227631617858</v>
+      </c>
+      <c r="I4" s="314" t="s">
+        <v>158</v>
+      </c>
+      <c r="J4" s="314"/>
+      <c r="K4"/>
+      <c r="L4"/>
+      <c r="M4"/>
+      <c r="N4"/>
+      <c r="O4"/>
+      <c r="P4"/>
+      <c r="Q4"/>
+    </row>
+    <row r="5" spans="2:17" ht="14.4">
       <c r="B5" s="228" t="s">
         <v>159</v>
       </c>
@@ -28532,10 +29948,29 @@
       <c r="E5" s="230">
         <v>525</v>
       </c>
-      <c r="F5" s="230"/>
-      <c r="G5" s="230"/>
-    </row>
-    <row r="6" spans="2:7">
+      <c r="F5" s="227">
+        <f t="shared" si="0"/>
+        <v>523.08157499779293</v>
+      </c>
+      <c r="G5" s="227">
+        <f t="shared" si="1"/>
+        <v>3.6803544890932072</v>
+      </c>
+      <c r="I5" s="311" t="s">
+        <v>160</v>
+      </c>
+      <c r="J5" s="311">
+        <v>0.98928820282730667</v>
+      </c>
+      <c r="K5"/>
+      <c r="L5"/>
+      <c r="M5"/>
+      <c r="N5"/>
+      <c r="O5"/>
+      <c r="P5"/>
+      <c r="Q5"/>
+    </row>
+    <row r="6" spans="2:17" ht="14.4">
       <c r="B6" s="228" t="s">
         <v>161</v>
       </c>
@@ -28548,10 +29983,29 @@
       <c r="E6" s="230">
         <v>670</v>
       </c>
-      <c r="F6" s="230"/>
-      <c r="G6" s="230"/>
-    </row>
-    <row r="7" spans="2:7" ht="14.4" thickBot="1">
+      <c r="F6" s="227">
+        <f t="shared" si="0"/>
+        <v>660.08960889909076</v>
+      </c>
+      <c r="G6" s="227">
+        <f t="shared" si="1"/>
+        <v>98.215851772980997</v>
+      </c>
+      <c r="I6" s="311" t="s">
+        <v>162</v>
+      </c>
+      <c r="J6" s="311">
+        <v>0.97869114825328229</v>
+      </c>
+      <c r="K6"/>
+      <c r="L6"/>
+      <c r="M6"/>
+      <c r="N6"/>
+      <c r="O6"/>
+      <c r="P6"/>
+      <c r="Q6"/>
+    </row>
+    <row r="7" spans="2:17" ht="15" thickBot="1">
       <c r="B7" s="232" t="s">
         <v>163</v>
       </c>
@@ -28564,14 +30018,63 @@
       <c r="E7" s="234">
         <v>490</v>
       </c>
-      <c r="F7" s="234"/>
-      <c r="G7" s="234"/>
-    </row>
-    <row r="8" spans="2:7" ht="14.4" thickBot="1">
-      <c r="G8" s="235"/>
-    </row>
-    <row r="9" spans="2:7" ht="14.4" thickBot="1"/>
-    <row r="10" spans="2:7" ht="14.4" thickBot="1">
+      <c r="F7" s="227">
+        <f t="shared" si="0"/>
+        <v>482.25655513375125</v>
+      </c>
+      <c r="G7" s="227">
+        <f t="shared" si="1"/>
+        <v>59.960938396634141</v>
+      </c>
+      <c r="I7" s="311" t="s">
+        <v>164</v>
+      </c>
+      <c r="J7" s="311">
+        <v>0.95738229650656459</v>
+      </c>
+      <c r="K7"/>
+      <c r="L7"/>
+      <c r="M7"/>
+      <c r="N7"/>
+      <c r="O7"/>
+      <c r="P7"/>
+      <c r="Q7"/>
+    </row>
+    <row r="8" spans="2:17" ht="15" thickBot="1">
+      <c r="G8" s="235">
+        <f>SUM(G3:G7)</f>
+        <v>392.50904917453994</v>
+      </c>
+      <c r="I8" s="311" t="s">
+        <v>165</v>
+      </c>
+      <c r="J8" s="311">
+        <v>14.009087214635695</v>
+      </c>
+      <c r="K8"/>
+      <c r="L8"/>
+      <c r="M8"/>
+      <c r="N8"/>
+      <c r="O8"/>
+      <c r="P8"/>
+      <c r="Q8"/>
+    </row>
+    <row r="9" spans="2:17" ht="15" thickBot="1">
+      <c r="I9" s="312" t="s">
+        <v>166</v>
+      </c>
+      <c r="J9" s="312">
+        <v>5</v>
+      </c>
+      <c r="K9"/>
+      <c r="L9"/>
+      <c r="M9"/>
+      <c r="N9"/>
+      <c r="O9"/>
+      <c r="P9"/>
+      <c r="Q9"/>
+    </row>
+    <row r="10" spans="2:17" ht="15" thickBot="1">
       <c r="B10" s="237" t="s">
         <v>152</v>
       </c>
@@ -28581,25 +30084,287 @@
       <c r="D10" s="222" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="11" spans="2:7">
+      <c r="I10"/>
+      <c r="J10"/>
+      <c r="K10"/>
+      <c r="L10"/>
+      <c r="M10"/>
+      <c r="N10"/>
+      <c r="O10"/>
+      <c r="P10"/>
+      <c r="Q10"/>
+    </row>
+    <row r="11" spans="2:17" ht="15" thickBot="1">
       <c r="B11" s="238">
         <v>3</v>
       </c>
       <c r="C11" s="181">
         <v>25</v>
       </c>
-      <c r="D11" s="227"/>
-    </row>
-    <row r="12" spans="2:7" ht="14.4" thickBot="1">
+      <c r="D11" s="227">
+        <f>$J$18+$J$19*B11+$J$20*C11</f>
+        <v>581.43462523174719</v>
+      </c>
+      <c r="I11" t="s">
+        <v>167</v>
+      </c>
+      <c r="J11"/>
+      <c r="K11"/>
+      <c r="L11"/>
+      <c r="M11"/>
+      <c r="N11"/>
+      <c r="O11"/>
+      <c r="P11"/>
+      <c r="Q11"/>
+    </row>
+    <row r="12" spans="2:17" ht="15" thickBot="1">
       <c r="B12" s="239">
         <v>2.6</v>
       </c>
       <c r="C12" s="183">
         <v>26</v>
       </c>
-      <c r="D12" s="234"/>
+      <c r="D12" s="227">
+        <f>$J$18+$J$19*B12+$J$20*C12</f>
+        <v>560.91153880109482</v>
+      </c>
       <c r="G12" s="240"/>
+      <c r="I12" s="313"/>
+      <c r="J12" s="313" t="s">
+        <v>168</v>
+      </c>
+      <c r="K12" s="313" t="s">
+        <v>169</v>
+      </c>
+      <c r="L12" s="313" t="s">
+        <v>170</v>
+      </c>
+      <c r="M12" s="313" t="s">
+        <v>171</v>
+      </c>
+      <c r="N12" s="313" t="s">
+        <v>172</v>
+      </c>
+      <c r="O12"/>
+      <c r="P12"/>
+      <c r="Q12"/>
+    </row>
+    <row r="13" spans="2:17" ht="14.4">
+      <c r="I13" s="311" t="s">
+        <v>173</v>
+      </c>
+      <c r="J13" s="311">
+        <v>2</v>
+      </c>
+      <c r="K13" s="311">
+        <v>18027.49095082546</v>
+      </c>
+      <c r="L13" s="311">
+        <v>9013.7454754127302</v>
+      </c>
+      <c r="M13" s="311">
+        <v>45.928854350588743</v>
+      </c>
+      <c r="N13" s="311">
+        <v>2.1308851746717622E-2</v>
+      </c>
+      <c r="O13"/>
+      <c r="P13"/>
+      <c r="Q13"/>
+    </row>
+    <row r="14" spans="2:17" ht="14.4">
+      <c r="I14" s="311" t="s">
+        <v>174</v>
+      </c>
+      <c r="J14" s="311">
+        <v>2</v>
+      </c>
+      <c r="K14" s="318">
+        <v>392.50904917453863</v>
+      </c>
+      <c r="L14" s="311">
+        <v>196.25452458726932</v>
+      </c>
+      <c r="M14" s="311"/>
+      <c r="N14" s="311"/>
+      <c r="O14"/>
+      <c r="P14"/>
+      <c r="Q14"/>
+    </row>
+    <row r="15" spans="2:17" ht="15" thickBot="1">
+      <c r="I15" s="312" t="s">
+        <v>59</v>
+      </c>
+      <c r="J15" s="312">
+        <v>4</v>
+      </c>
+      <c r="K15" s="312">
+        <v>18420</v>
+      </c>
+      <c r="L15" s="312"/>
+      <c r="M15" s="312"/>
+      <c r="N15" s="312"/>
+      <c r="O15"/>
+      <c r="P15"/>
+      <c r="Q15"/>
+    </row>
+    <row r="16" spans="2:17" ht="15" thickBot="1">
+      <c r="I16"/>
+      <c r="J16"/>
+      <c r="K16"/>
+      <c r="L16"/>
+      <c r="M16"/>
+      <c r="N16"/>
+      <c r="O16"/>
+      <c r="P16"/>
+      <c r="Q16"/>
+    </row>
+    <row r="17" spans="9:17" ht="14.4">
+      <c r="I17" s="313"/>
+      <c r="J17" s="313" t="s">
+        <v>175</v>
+      </c>
+      <c r="K17" s="313" t="s">
+        <v>165</v>
+      </c>
+      <c r="L17" s="313" t="s">
+        <v>176</v>
+      </c>
+      <c r="M17" s="313" t="s">
+        <v>177</v>
+      </c>
+      <c r="N17" s="313" t="s">
+        <v>178</v>
+      </c>
+      <c r="O17" s="313" t="s">
+        <v>179</v>
+      </c>
+      <c r="P17" s="313" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q17" s="313" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="18" spans="9:17" ht="14.4">
+      <c r="I18" s="311" t="s">
+        <v>182</v>
+      </c>
+      <c r="J18" s="315">
+        <v>-44.81018804626126</v>
+      </c>
+      <c r="K18" s="311">
+        <v>69.246866630890381</v>
+      </c>
+      <c r="L18" s="311">
+        <v>-0.64710780756499753</v>
+      </c>
+      <c r="M18" s="311">
+        <v>0.58391574508017841</v>
+      </c>
+      <c r="N18" s="311">
+        <v>-342.75540778225883</v>
+      </c>
+      <c r="O18" s="311">
+        <v>253.13503168973631</v>
+      </c>
+      <c r="P18" s="311">
+        <v>-342.75540778225883</v>
+      </c>
+      <c r="Q18" s="311">
+        <v>253.13503168973631</v>
+      </c>
+    </row>
+    <row r="19" spans="9:17" ht="14.4">
+      <c r="I19" s="311" t="s">
+        <v>152</v>
+      </c>
+      <c r="J19" s="316">
+        <v>87.640151849563026</v>
+      </c>
+      <c r="K19" s="311">
+        <v>15.237186664924886</v>
+      </c>
+      <c r="L19" s="311">
+        <v>5.7517279125618073</v>
+      </c>
+      <c r="M19" s="311">
+        <v>2.8922600815111749E-2</v>
+      </c>
+      <c r="N19" s="311">
+        <v>22.079829052021836</v>
+      </c>
+      <c r="O19" s="311">
+        <v>153.20047464710422</v>
+      </c>
+      <c r="P19" s="311">
+        <v>22.079829052021836</v>
+      </c>
+      <c r="Q19" s="311">
+        <v>153.20047464710422</v>
+      </c>
+    </row>
+    <row r="20" spans="9:17" ht="15" thickBot="1">
+      <c r="I20" s="312" t="s">
+        <v>153</v>
+      </c>
+      <c r="J20" s="317">
+        <v>14.532974309172776</v>
+      </c>
+      <c r="K20" s="312">
+        <v>2.9137375361504319</v>
+      </c>
+      <c r="L20" s="312">
+        <v>4.9877431061870565</v>
+      </c>
+      <c r="M20" s="312">
+        <v>3.7924876930238542E-2</v>
+      </c>
+      <c r="N20" s="312">
+        <v>1.9961735454816427</v>
+      </c>
+      <c r="O20" s="312">
+        <v>27.069775072863909</v>
+      </c>
+      <c r="P20" s="312">
+        <v>1.9961735454816427</v>
+      </c>
+      <c r="Q20" s="312">
+        <v>27.069775072863909</v>
+      </c>
+    </row>
+    <row r="21" spans="9:17" ht="14.4">
+      <c r="I21"/>
+      <c r="J21"/>
+      <c r="K21"/>
+      <c r="L21"/>
+      <c r="M21"/>
+      <c r="N21"/>
+      <c r="O21"/>
+      <c r="P21"/>
+      <c r="Q21"/>
+    </row>
+    <row r="22" spans="9:17" ht="14.4">
+      <c r="I22"/>
+      <c r="J22"/>
+      <c r="K22"/>
+      <c r="L22"/>
+      <c r="M22"/>
+      <c r="N22"/>
+      <c r="O22"/>
+      <c r="P22"/>
+      <c r="Q22"/>
+    </row>
+    <row r="23" spans="9:17" ht="14.4">
+      <c r="I23"/>
+      <c r="J23"/>
+      <c r="K23"/>
+      <c r="L23"/>
+      <c r="M23"/>
+      <c r="N23"/>
+      <c r="O23"/>
+      <c r="P23"/>
+      <c r="Q23"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -30520,10 +32285,10 @@
       </c>
     </row>
     <row r="61" spans="2:22">
-      <c r="H61" s="281" t="s">
+      <c r="H61" s="291" t="s">
         <v>63</v>
       </c>
-      <c r="I61" s="281"/>
+      <c r="I61" s="291"/>
       <c r="T61" s="1" t="s">
         <v>64</v>
       </c>
@@ -30606,7 +32371,7 @@
     <mergeCell ref="H61:I61"/>
   </mergeCells>
   <conditionalFormatting sqref="X4:AC17">
-    <cfRule type="expression" dxfId="10" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>$AC4="No - 0"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -30661,11 +32426,11 @@
       <c r="H1" s="67" t="s">
         <v>74</v>
       </c>
-      <c r="J1" s="282" t="s">
+      <c r="J1" s="292" t="s">
         <v>76</v>
       </c>
-      <c r="K1" s="282"/>
-      <c r="L1" s="282"/>
+      <c r="K1" s="292"/>
+      <c r="L1" s="292"/>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="251">
@@ -31148,10 +32913,10 @@
     <mergeCell ref="J1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="F2:F16">
-    <cfRule type="top10" dxfId="9" priority="2" bottom="1" rank="5"/>
+    <cfRule type="top10" dxfId="5" priority="2" bottom="1" rank="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H16">
-    <cfRule type="top10" dxfId="8" priority="1" bottom="1" rank="5"/>
+    <cfRule type="top10" dxfId="4" priority="1" bottom="1" rank="5"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" r:id="rId1"/>

--- a/Classwork_ML.xlsx
+++ b/Classwork_ML.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git Backup\2GITHUB\Secure-Meter-Classwork\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71AC0150-5441-4543-8E3C-DAEACC2E0F07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87F29B8D-0A58-4C4A-A13D-BC356626B794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="823" firstSheet="3" activeTab="4" xr2:uid="{8906883F-2923-499F-A745-AA2DCE968BC0}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="823" firstSheet="6" activeTab="13" xr2:uid="{8906883F-2923-499F-A745-AA2DCE968BC0}"/>
   </bookViews>
   <sheets>
     <sheet name="Forecast Sheet" sheetId="16" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1066" uniqueCount="227">
   <si>
     <t>Day</t>
   </si>
@@ -935,12 +935,19 @@
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1986,653 +1993,654 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="319">
+  <cellXfs count="320">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="37" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="39" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="45" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="46" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="45" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="37" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="51" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="56" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="57" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="35" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="37" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="39" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="56" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="57" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="21" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="25" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="29" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="30" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="53" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="37" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="37" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="34" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="2" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="6" borderId="8" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="2" fillId="6" borderId="10" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="6" borderId="5" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="46" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="40" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="62" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="42" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="37" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="39" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="44" xfId="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="45" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="46" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="45" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="48" xfId="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="50" xfId="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="37" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="51" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="52" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="53" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="54" xfId="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="56" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="57" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="58" xfId="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="58" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="34" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="36" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="38" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="61" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="44" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="35" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="44" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="35" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="37" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="39" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="58" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="56" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="57" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="21" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="25" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="29" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="30" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="53" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="50" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="37" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="37" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="36" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="38" xfId="2" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="6" borderId="8" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="1" fillId="6" borderId="10" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="6" borderId="5" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="46" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="40" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="62" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="2" borderId="62" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="42" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="19" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="34" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="36" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="38" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="44" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="39" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="44" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="10" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="63" xfId="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="11" borderId="59" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="11" borderId="6" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="11" borderId="8" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="9" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="9" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="11" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="1" fillId="11" borderId="10" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="11" borderId="5" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="4" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="11" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="12" xfId="2" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="49" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="11" borderId="59" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="11" borderId="6" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="7" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="11" borderId="8" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="9" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="11" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="2" fillId="11" borderId="10" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="11" borderId="5" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="4" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="12" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="59" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="12" xfId="2" applyFill="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="60" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="49" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="48" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4076,6 +4084,452 @@
     <a:ln w="28575" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:srgbClr val="C00000"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="20" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="50000"/>
+                    <a:lumOff val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>ROC Curve</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:alpha val="70000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:prstDash val="sysDot"/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:gradFill rotWithShape="1">
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="accent2">
+                      <a:lumMod val="110000"/>
+                      <a:satMod val="105000"/>
+                      <a:tint val="67000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="50000">
+                    <a:schemeClr val="accent2">
+                      <a:lumMod val="105000"/>
+                      <a:satMod val="103000"/>
+                      <a:tint val="73000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="accent2">
+                      <a:lumMod val="105000"/>
+                      <a:satMod val="109000"/>
+                      <a:tint val="81000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:schemeClr val="accent2">
+                    <a:shade val="95000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>ROC!$E$15:$K$15</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.16666666666666666</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.16666666666666666</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.33333333333333331</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>ROC!$E$16:$K$16</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-501D-496F-A0D4-C4DDF827FC6D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1097208560"/>
+        <c:axId val="1042294400"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1097208560"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="dk1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>False Positive Rate (FPR=FP/N=FP/(FP+TN))</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="dk1">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1042294400"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1042294400"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="dk1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>True Positive Rate (TPR=TP/P=TP/(TP+FN))</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="dk1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1097208560"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="lt1">
+                <a:lumMod val="95000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1">
+                <a:alpha val="0"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="lt1"/>
+    </a:solidFill>
+    <a:ln w="28575" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
@@ -8546,11 +9000,11 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="20" baseline="0">
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="dk1">
-                    <a:lumMod val="50000"/>
-                    <a:lumOff val="50000"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -8559,8 +9013,8 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>ROC Curve</a:t>
+              <a:rPr lang="en-IN"/>
+              <a:t>Var-1 vs. Var-2</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -8573,6 +9027,26 @@
         </a:ln>
         <a:effectLst/>
       </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -8583,14 +9057,12 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
+          <c:tx>
+            <c:v>Var-1 vs. Var-2</c:v>
+          </c:tx>
           <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:alpha val="70000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:prstDash val="sysDot"/>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -8599,68 +9071,119 @@
             <c:symbol val="circle"/>
             <c:size val="5"/>
             <c:spPr>
-              <a:gradFill rotWithShape="1">
-                <a:gsLst>
-                  <a:gs pos="0">
-                    <a:schemeClr val="accent2">
-                      <a:lumMod val="110000"/>
-                      <a:satMod val="105000"/>
-                      <a:tint val="67000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="50000">
-                    <a:schemeClr val="accent2">
-                      <a:lumMod val="105000"/>
-                      <a:satMod val="103000"/>
-                      <a:tint val="73000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="100000">
-                    <a:schemeClr val="accent2">
-                      <a:lumMod val="105000"/>
-                      <a:satMod val="109000"/>
-                      <a:tint val="81000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                </a:gsLst>
-                <a:lin ang="5400000" scaled="0"/>
-              </a:gradFill>
-              <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
                 <a:solidFill>
-                  <a:schemeClr val="accent2">
-                    <a:shade val="95000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="accent1"/>
                 </a:solidFill>
-                <a:round/>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>ROC!$E$15:$K$15</c:f>
+              <c:f>'K-Means Clustering (2)'!$C$4:$C$10</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.16666666666666666</c:v>
+                  <c:v>1.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.16666666666666666</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.33333333333333331</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.5</c:v>
+                  <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.5</c:v>
+                  <c:v>4.5</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>3.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'K-Means Clustering (2)'!$D$4:$D$10</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9D59-4F74-BD8A-07FA72416FF4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Centroid-1</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'K-Means Clustering (2)'!$C$4</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -8668,29 +9191,11 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>ROC!$E$16:$K$16</c:f>
+              <c:f>'K-Means Clustering (2)'!$D$4</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0.2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.6</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.8</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.8</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="6">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -8699,7 +9204,369 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-501D-496F-A0D4-C4DDF827FC6D}"/>
+              <c16:uniqueId val="{00000001-9D59-4F74-BD8A-07FA72416FF4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>Centroid-2</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'K-Means Clustering (2)'!$C$7</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'K-Means Clustering (2)'!$D$7</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-9D59-4F74-BD8A-07FA72416FF4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>Centroid-1-2</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'K-Means Clustering (2)'!$C$14</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1.8333333333333333</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'K-Means Clustering (2)'!$D$14</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2.3333333333333335</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-9D59-4F74-BD8A-07FA72416FF4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:v>Centroid-2-2</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'K-Means Clustering (2)'!$C$15</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>4.125</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'K-Means Clustering (2)'!$D$15</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>5.375</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-9D59-4F74-BD8A-07FA72416FF4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:v>Centroid-1-3</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'K-Means Clustering (2)'!$C$16</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1.25</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'K-Means Clustering (2)'!$D$16</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-9D59-4F74-BD8A-07FA72416FF4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:v>Centroid-2-3</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'K-Means Clustering (2)'!$C$17</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>3.9</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'K-Means Clustering (2)'!$D$17</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>5.0999999999999996</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-9D59-4F74-BD8A-07FA72416FF4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:v>Test Data Point</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'K-Means Clustering (2)'!$B$21</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'K-Means Clustering (2)'!$C$21</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-9D59-4F74-BD8A-07FA72416FF4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -8711,11 +9578,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1097208560"/>
-        <c:axId val="1042294400"/>
+        <c:axId val="1824140351"/>
+        <c:axId val="1606132367"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1097208560"/>
+        <c:axId val="1824140351"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8725,7 +9592,7 @@
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="dk1">
+                <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
                   <a:lumOff val="85000"/>
                 </a:schemeClr>
@@ -8735,147 +9602,15 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="dk1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>False Positive Rate (FPR=FP/N=FP/(FP+TN))</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:title>
         <c:numFmt formatCode="0.00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln w="9525" cap="rnd">
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
-              <a:schemeClr val="dk1">
-                <a:lumMod val="20000"/>
-                <a:lumOff val="80000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="dk1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1042294400"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="1042294400"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="dk1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="dk1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>True Positive Rate (TPR=TP/P=TP/(TP+FN))</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:title>
-        <c:numFmt formatCode="0.00" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="rnd">
-            <a:solidFill>
-              <a:schemeClr val="dk1">
+              <a:schemeClr val="tx1">
                 <a:lumMod val="25000"/>
                 <a:lumOff val="75000"/>
               </a:schemeClr>
@@ -8889,9 +9624,9 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="dk1">
+                  <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
@@ -8904,32 +9639,111 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1097208560"/>
+        <c:crossAx val="1606132367"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1606132367"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1824140351"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:spPr>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="100000">
-              <a:schemeClr val="lt1">
-                <a:lumMod val="95000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="0">
-              <a:schemeClr val="lt1">
-                <a:alpha val="0"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
+        <a:noFill/>
         <a:ln>
           <a:noFill/>
         </a:ln>
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -8943,11 +9757,11 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="bg1"/>
     </a:solidFill>
     <a:ln w="28575" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="tx1"/>
+        <a:srgbClr val="C00000"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
@@ -8958,7 +9772,7 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr b="1"/>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
     </a:p>
@@ -9252,6 +10066,46 @@
 </file>
 
 <file path=xl/charts/colors8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors9.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -13369,6 +14223,522 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style9.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -13405,6 +14775,98 @@
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>75174</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>72829</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>196069</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>109758</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10683D90-1368-4C75-9750-D229D6903276}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>182880</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>579630</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>137520</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{122220D7-70AF-8DD9-C54D-BC9C4976A4C4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6888480" y="3749040"/>
+          <a:ext cx="5883150" cy="4153260"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="C00000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -14370,6 +15832,47 @@
 
 <file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>355600</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27006767-6D7C-C4E8-7CFB-BD3D731C5A49}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
@@ -14436,98 +15939,6 @@
             </a14:hiddenFill>
           </a:ext>
         </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>75174</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>72829</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>196069</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>109758</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10683D90-1368-4C75-9750-D229D6903276}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>182880</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>579630</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>137520</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{122220D7-70AF-8DD9-C54D-BC9C4976A4C4}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6888480" y="3749040"/>
-          <a:ext cx="5883150" cy="4153260"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="28575">
-          <a:solidFill>
-            <a:srgbClr val="C00000"/>
-          </a:solidFill>
-        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -15217,11 +16628,11 @@
       <c r="H1" s="39" t="s">
         <v>74</v>
       </c>
-      <c r="J1" s="292" t="s">
+      <c r="J1" s="299" t="s">
         <v>76</v>
       </c>
-      <c r="K1" s="292"/>
-      <c r="L1" s="292"/>
+      <c r="K1" s="299"/>
+      <c r="L1" s="299"/>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="42">
@@ -15616,13 +17027,13 @@
 Distance],1)</f>
         <v>134</v>
       </c>
-      <c r="L2" s="293" t="s">
+      <c r="L2" s="300" t="s">
         <v>76</v>
       </c>
-      <c r="M2" s="293"/>
-      <c r="N2" s="293"/>
-      <c r="O2" s="293"/>
-      <c r="P2" s="293"/>
+      <c r="M2" s="300"/>
+      <c r="N2" s="300"/>
+      <c r="O2" s="300"/>
+      <c r="P2" s="300"/>
     </row>
     <row r="3" spans="1:17" s="179" customFormat="1" ht="13.8" customHeight="1" thickBot="1">
       <c r="A3" s="172">
@@ -21731,13 +23142,13 @@
       <c r="H2" s="84"/>
       <c r="I2" s="85"/>
       <c r="J2" s="82"/>
-      <c r="L2" s="293" t="s">
+      <c r="L2" s="300" t="s">
         <v>76</v>
       </c>
-      <c r="M2" s="293"/>
-      <c r="N2" s="293"/>
-      <c r="O2" s="293"/>
-      <c r="P2" s="293"/>
+      <c r="M2" s="300"/>
+      <c r="N2" s="300"/>
+      <c r="O2" s="300"/>
+      <c r="P2" s="300"/>
     </row>
     <row r="3" spans="1:17" ht="15" thickBot="1">
       <c r="A3" s="86">
@@ -25379,18 +26790,18 @@
   <sheetData>
     <row r="1" spans="2:15" ht="15" thickBot="1"/>
     <row r="2" spans="2:15" ht="15" thickBot="1">
-      <c r="E2" s="294" t="s">
+      <c r="E2" s="301" t="s">
         <v>92</v>
       </c>
-      <c r="F2" s="295"/>
-      <c r="H2" s="294" t="s">
+      <c r="F2" s="302"/>
+      <c r="H2" s="301" t="s">
         <v>92</v>
       </c>
-      <c r="I2" s="295"/>
-      <c r="K2" s="294" t="s">
+      <c r="I2" s="302"/>
+      <c r="K2" s="301" t="s">
         <v>92</v>
       </c>
-      <c r="L2" s="295"/>
+      <c r="L2" s="302"/>
       <c r="O2" s="24" t="s">
         <v>201</v>
       </c>
@@ -25838,10 +27249,10 @@
       </c>
     </row>
     <row r="19" spans="2:6" ht="15" thickBot="1">
-      <c r="B19" s="296" t="s">
+      <c r="B19" s="303" t="s">
         <v>108</v>
       </c>
-      <c r="C19" s="296"/>
+      <c r="C19" s="303"/>
     </row>
     <row r="20" spans="2:6" ht="15" thickBot="1">
       <c r="B20" s="117" t="s">
@@ -25897,7 +27308,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{272A9744-6985-4D62-8438-692B3A8F9A0C}">
-  <dimension ref="B1:M21"/>
+  <dimension ref="B1:M23"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="5" width="8.88671875" style="1"/>
@@ -25911,18 +27322,18 @@
   <sheetData>
     <row r="1" spans="2:13" ht="15" thickBot="1"/>
     <row r="2" spans="2:13" ht="15" thickBot="1">
-      <c r="E2" s="294" t="s">
+      <c r="E2" s="301" t="s">
         <v>92</v>
       </c>
-      <c r="F2" s="295"/>
-      <c r="H2" s="294" t="s">
+      <c r="F2" s="302"/>
+      <c r="H2" s="301" t="s">
         <v>92</v>
       </c>
-      <c r="I2" s="295"/>
-      <c r="K2" s="294" t="s">
+      <c r="I2" s="302"/>
+      <c r="K2" s="301" t="s">
         <v>92</v>
       </c>
-      <c r="L2" s="295"/>
+      <c r="L2" s="302"/>
     </row>
     <row r="3" spans="2:13" ht="15" thickBot="1">
       <c r="B3" s="104" t="s">
@@ -25972,17 +27383,44 @@
       <c r="D4" s="108">
         <v>1</v>
       </c>
-      <c r="E4" s="272"/>
-      <c r="F4" s="273"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="272"/>
-      <c r="I4" s="273"/>
-      <c r="J4" s="274"/>
-      <c r="K4" s="273"/>
-      <c r="L4" s="273"/>
-      <c r="M4" s="274"/>
-    </row>
-    <row r="5" spans="2:13">
+      <c r="E4" s="272">
+        <f>SQRT((C4-$C$12)^2+(D4-$D$12)^2)</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="273">
+        <f>SQRT((C4-$C$13)^2+(D4-$D$13)^2)</f>
+        <v>7.2111025509279782</v>
+      </c>
+      <c r="G4" s="274" t="str">
+        <f>IF(E4&lt;=F4,"C-1","C-2")</f>
+        <v>C-1</v>
+      </c>
+      <c r="H4" s="272">
+        <f>SQRT((C4-$C$14)^2+(D4-$D$14)^2)</f>
+        <v>1.5723301886761007</v>
+      </c>
+      <c r="I4" s="273">
+        <f>SQRT((C4-$C$15)^2+(D4-$D$15)^2)</f>
+        <v>5.3764532919016421</v>
+      </c>
+      <c r="J4" s="274" t="str">
+        <f>IF(H4&lt;=I4,"C-1","C-2")</f>
+        <v>C-1</v>
+      </c>
+      <c r="K4" s="272">
+        <f>SQRT((C4-$C$16)^2+(D4-$D$16)^2)</f>
+        <v>0.55901699437494745</v>
+      </c>
+      <c r="L4" s="273">
+        <f>SQRT((C4-$C$17)^2+(D4-$D$17)^2)</f>
+        <v>5.0219518117958879</v>
+      </c>
+      <c r="M4" s="274" t="str">
+        <f>IF(K4&lt;=L4,"C-1","C-2")</f>
+        <v>C-1</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13" ht="15" thickBot="1">
       <c r="B5" s="106">
         <v>2</v>
       </c>
@@ -25992,16 +27430,44 @@
       <c r="D5" s="108">
         <v>2</v>
       </c>
-      <c r="E5" s="275"/>
-      <c r="F5" s="280"/>
-      <c r="H5" s="275"/>
-      <c r="I5" s="280"/>
-      <c r="J5" s="276"/>
-      <c r="K5" s="280"/>
-      <c r="L5" s="280"/>
-      <c r="M5" s="276"/>
-    </row>
-    <row r="6" spans="2:13">
+      <c r="E5" s="275">
+        <f t="shared" ref="E5:E10" si="0">SQRT((C5-$C$12)^2+(D5-$D$12)^2)</f>
+        <v>1.1180339887498949</v>
+      </c>
+      <c r="F5" s="319">
+        <f t="shared" ref="F5:F10" si="1">SQRT((C5-$C$13)^2+(D5-$D$13)^2)</f>
+        <v>6.103277807866851</v>
+      </c>
+      <c r="G5" s="276" t="str">
+        <f t="shared" ref="G5:G10" si="2">IF(E5&lt;=F5,"C-1","C-2")</f>
+        <v>C-1</v>
+      </c>
+      <c r="H5" s="277">
+        <f t="shared" ref="H5:H10" si="3">SQRT((C5-$C$14)^2+(D5-$D$14)^2)</f>
+        <v>0.47140452079103173</v>
+      </c>
+      <c r="I5" s="278">
+        <f t="shared" ref="I5:I10" si="4">SQRT((C5-$C$15)^2+(D5-$D$15)^2)</f>
+        <v>4.2756578441217679</v>
+      </c>
+      <c r="J5" s="279" t="str">
+        <f t="shared" ref="J5:J10" si="5">IF(H5&lt;=I5,"C-1","C-2")</f>
+        <v>C-1</v>
+      </c>
+      <c r="K5" s="277">
+        <f t="shared" ref="K5:K10" si="6">SQRT((C5-$C$16)^2+(D5-$D$16)^2)</f>
+        <v>0.55901699437494745</v>
+      </c>
+      <c r="L5" s="278">
+        <f t="shared" ref="L5:L10" si="7">SQRT((C5-$C$17)^2+(D5-$D$17)^2)</f>
+        <v>3.9204591567825315</v>
+      </c>
+      <c r="M5" s="279" t="str">
+        <f t="shared" ref="M5:M10" si="8">IF(K5&lt;=L5,"C-1","C-2")</f>
+        <v>C-1</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" ht="15" thickBot="1">
       <c r="B6" s="106">
         <v>3</v>
       </c>
@@ -26011,14 +27477,42 @@
       <c r="D6" s="108">
         <v>4</v>
       </c>
-      <c r="E6" s="275"/>
-      <c r="F6" s="280"/>
-      <c r="H6" s="275"/>
-      <c r="I6" s="280"/>
-      <c r="J6" s="276"/>
-      <c r="K6" s="280"/>
-      <c r="L6" s="280"/>
-      <c r="M6" s="276"/>
+      <c r="E6" s="277">
+        <f t="shared" si="0"/>
+        <v>3.6055512754639891</v>
+      </c>
+      <c r="F6" s="278">
+        <f t="shared" si="1"/>
+        <v>3.6055512754639891</v>
+      </c>
+      <c r="G6" s="279" t="str">
+        <f t="shared" si="2"/>
+        <v>C-1</v>
+      </c>
+      <c r="H6" s="275">
+        <f t="shared" si="3"/>
+        <v>2.0344259359556172</v>
+      </c>
+      <c r="I6" s="280">
+        <f t="shared" si="4"/>
+        <v>1.7765838004439869</v>
+      </c>
+      <c r="J6" s="276" t="str">
+        <f t="shared" si="5"/>
+        <v>C-2</v>
+      </c>
+      <c r="K6" s="280">
+        <f t="shared" si="6"/>
+        <v>3.0516389039334255</v>
+      </c>
+      <c r="L6" s="280">
+        <f t="shared" si="7"/>
+        <v>1.4212670403551892</v>
+      </c>
+      <c r="M6" s="276" t="str">
+        <f t="shared" si="8"/>
+        <v>C-2</v>
+      </c>
     </row>
     <row r="7" spans="2:13">
       <c r="B7" s="106">
@@ -26030,14 +27524,42 @@
       <c r="D7" s="108">
         <v>7</v>
       </c>
-      <c r="E7" s="275"/>
-      <c r="F7" s="280"/>
-      <c r="H7" s="275"/>
-      <c r="I7" s="280"/>
-      <c r="J7" s="276"/>
-      <c r="K7" s="280"/>
-      <c r="L7" s="280"/>
-      <c r="M7" s="276"/>
+      <c r="E7" s="275">
+        <f t="shared" si="0"/>
+        <v>7.2111025509279782</v>
+      </c>
+      <c r="F7" s="280">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G7" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>C-2</v>
+      </c>
+      <c r="H7" s="275">
+        <f t="shared" si="3"/>
+        <v>5.6396414385628768</v>
+      </c>
+      <c r="I7" s="280">
+        <f t="shared" si="4"/>
+        <v>1.845602882529175</v>
+      </c>
+      <c r="J7" s="276" t="str">
+        <f t="shared" si="5"/>
+        <v>C-2</v>
+      </c>
+      <c r="K7" s="280">
+        <f t="shared" si="6"/>
+        <v>6.656763477847174</v>
+      </c>
+      <c r="L7" s="280">
+        <f t="shared" si="7"/>
+        <v>2.1954498400100153</v>
+      </c>
+      <c r="M7" s="276" t="str">
+        <f t="shared" si="8"/>
+        <v>C-2</v>
+      </c>
     </row>
     <row r="8" spans="2:13">
       <c r="B8" s="106">
@@ -26049,14 +27571,42 @@
       <c r="D8" s="108">
         <v>5</v>
       </c>
-      <c r="E8" s="275"/>
-      <c r="F8" s="280"/>
-      <c r="H8" s="275"/>
-      <c r="I8" s="280"/>
-      <c r="J8" s="276"/>
-      <c r="K8" s="280"/>
-      <c r="L8" s="280"/>
-      <c r="M8" s="276"/>
+      <c r="E8" s="275">
+        <f t="shared" si="0"/>
+        <v>4.7169905660283016</v>
+      </c>
+      <c r="F8" s="280">
+        <f t="shared" si="1"/>
+        <v>2.5</v>
+      </c>
+      <c r="G8" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>C-2</v>
+      </c>
+      <c r="H8" s="275">
+        <f t="shared" si="3"/>
+        <v>3.1446603773522015</v>
+      </c>
+      <c r="I8" s="280">
+        <f t="shared" si="4"/>
+        <v>0.72886898685566259</v>
+      </c>
+      <c r="J8" s="276" t="str">
+        <f t="shared" si="5"/>
+        <v>C-2</v>
+      </c>
+      <c r="K8" s="280">
+        <f t="shared" si="6"/>
+        <v>4.1608292442733097</v>
+      </c>
+      <c r="L8" s="280">
+        <f t="shared" si="7"/>
+        <v>0.41231056256176585</v>
+      </c>
+      <c r="M8" s="276" t="str">
+        <f t="shared" si="8"/>
+        <v>C-2</v>
+      </c>
     </row>
     <row r="9" spans="2:13">
       <c r="B9" s="106">
@@ -26068,14 +27618,42 @@
       <c r="D9" s="108">
         <v>5</v>
       </c>
-      <c r="E9" s="275"/>
-      <c r="F9" s="280"/>
-      <c r="H9" s="275"/>
-      <c r="I9" s="280"/>
-      <c r="J9" s="276"/>
-      <c r="K9" s="280"/>
-      <c r="L9" s="280"/>
-      <c r="M9" s="276"/>
+      <c r="E9" s="275">
+        <f t="shared" si="0"/>
+        <v>5.315072906367325</v>
+      </c>
+      <c r="F9" s="280">
+        <f t="shared" si="1"/>
+        <v>2.0615528128088303</v>
+      </c>
+      <c r="G9" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>C-2</v>
+      </c>
+      <c r="H9" s="275">
+        <f t="shared" si="3"/>
+        <v>3.7712361663282534</v>
+      </c>
+      <c r="I9" s="280">
+        <f t="shared" si="4"/>
+        <v>0.5303300858899106</v>
+      </c>
+      <c r="J9" s="276" t="str">
+        <f t="shared" si="5"/>
+        <v>C-2</v>
+      </c>
+      <c r="K9" s="280">
+        <f t="shared" si="6"/>
+        <v>4.7762432936356998</v>
+      </c>
+      <c r="L9" s="280">
+        <f t="shared" si="7"/>
+        <v>0.60827625302982202</v>
+      </c>
+      <c r="M9" s="276" t="str">
+        <f t="shared" si="8"/>
+        <v>C-2</v>
+      </c>
     </row>
     <row r="10" spans="2:13" ht="15" thickBot="1">
       <c r="B10" s="109">
@@ -26087,15 +27665,42 @@
       <c r="D10" s="111">
         <v>4.5</v>
       </c>
-      <c r="E10" s="277"/>
-      <c r="F10" s="278"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="277"/>
-      <c r="I10" s="278"/>
-      <c r="J10" s="279"/>
-      <c r="K10" s="278"/>
-      <c r="L10" s="278"/>
-      <c r="M10" s="279"/>
+      <c r="E10" s="277">
+        <f t="shared" si="0"/>
+        <v>4.3011626335213133</v>
+      </c>
+      <c r="F10" s="278">
+        <f t="shared" si="1"/>
+        <v>2.9154759474226504</v>
+      </c>
+      <c r="G10" s="29" t="str">
+        <f t="shared" si="2"/>
+        <v>C-2</v>
+      </c>
+      <c r="H10" s="277">
+        <f t="shared" si="3"/>
+        <v>2.733536577809454</v>
+      </c>
+      <c r="I10" s="278">
+        <f t="shared" si="4"/>
+        <v>1.0752906583803283</v>
+      </c>
+      <c r="J10" s="279" t="str">
+        <f t="shared" si="5"/>
+        <v>C-2</v>
+      </c>
+      <c r="K10" s="278">
+        <f t="shared" si="6"/>
+        <v>3.75</v>
+      </c>
+      <c r="L10" s="278">
+        <f t="shared" si="7"/>
+        <v>0.72111025509279758</v>
+      </c>
+      <c r="M10" s="279" t="str">
+        <f t="shared" si="8"/>
+        <v>C-2</v>
+      </c>
     </row>
     <row r="11" spans="2:13" ht="15" thickBot="1"/>
     <row r="12" spans="2:13">
@@ -26124,35 +27729,59 @@
       <c r="B14" s="112" t="s">
         <v>104</v>
       </c>
-      <c r="C14" s="113"/>
-      <c r="D14" s="114"/>
+      <c r="C14" s="113">
+        <f>AVERAGE(C4:C6)</f>
+        <v>1.8333333333333333</v>
+      </c>
+      <c r="D14" s="114">
+        <f>AVERAGE(D4:D6)</f>
+        <v>2.3333333333333335</v>
+      </c>
     </row>
     <row r="15" spans="2:13" ht="15" thickBot="1">
       <c r="B15" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="C15" s="110"/>
-      <c r="D15" s="115"/>
+      <c r="C15" s="110">
+        <f>AVERAGE(C7:C10)</f>
+        <v>4.125</v>
+      </c>
+      <c r="D15" s="115">
+        <f>AVERAGE(D7:D10)</f>
+        <v>5.375</v>
+      </c>
     </row>
     <row r="16" spans="2:13">
       <c r="B16" s="112" t="s">
         <v>106</v>
       </c>
-      <c r="C16" s="107"/>
-      <c r="D16" s="116"/>
+      <c r="C16" s="107">
+        <f>AVERAGE(C4:C5)</f>
+        <v>1.25</v>
+      </c>
+      <c r="D16" s="116">
+        <f>AVERAGE(D4:D5)</f>
+        <v>1.5</v>
+      </c>
     </row>
     <row r="17" spans="2:6" ht="15" thickBot="1">
       <c r="B17" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="C17" s="110"/>
-      <c r="D17" s="115"/>
+      <c r="C17" s="110">
+        <f>AVERAGE(C6:C10)</f>
+        <v>3.9</v>
+      </c>
+      <c r="D17" s="115">
+        <f>AVERAGE(D6:D10)</f>
+        <v>5.0999999999999996</v>
+      </c>
     </row>
     <row r="19" spans="2:6" ht="15" thickBot="1">
-      <c r="B19" s="296" t="s">
+      <c r="B19" s="303" t="s">
         <v>108</v>
       </c>
-      <c r="C19" s="296"/>
+      <c r="C19" s="303"/>
     </row>
     <row r="20" spans="2:6" ht="15" thickBot="1">
       <c r="B20" s="117" t="s">
@@ -26178,9 +27807,23 @@
       <c r="C21" s="121">
         <v>3</v>
       </c>
-      <c r="D21" s="121"/>
-      <c r="E21" s="121"/>
-      <c r="F21" s="122"/>
+      <c r="D21" s="121">
+        <f>SQRT((C16-B21)^2+(D16-C21)^2)</f>
+        <v>2.3048861143232218</v>
+      </c>
+      <c r="E21" s="121">
+        <f>SQRT((C17-B21)^2+(D17-C21)^2)</f>
+        <v>2.2847319317591719</v>
+      </c>
+      <c r="F21" s="122" t="str">
+        <f>IF(D21&lt;=E21,"C-1","C-2")</f>
+        <v>C-2</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6">
+      <c r="B23" s="318" t="s">
+        <v>201</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -26190,6 +27833,10 @@
     <mergeCell ref="B19:C19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="C14:D15 C16:D17" formulaRange="1"/>
+  </ignoredErrors>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -26211,19 +27858,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:19" ht="24" thickBot="1">
-      <c r="B1" s="297" t="s">
+      <c r="B1" s="304" t="s">
         <v>112</v>
       </c>
-      <c r="C1" s="298"/>
-      <c r="D1" s="298"/>
-      <c r="E1" s="298"/>
-      <c r="F1" s="298"/>
-      <c r="G1" s="298"/>
-      <c r="H1" s="298"/>
-      <c r="I1" s="298"/>
-      <c r="J1" s="298"/>
-      <c r="K1" s="298"/>
-      <c r="L1" s="299"/>
+      <c r="C1" s="305"/>
+      <c r="D1" s="305"/>
+      <c r="E1" s="305"/>
+      <c r="F1" s="305"/>
+      <c r="G1" s="305"/>
+      <c r="H1" s="305"/>
+      <c r="I1" s="305"/>
+      <c r="J1" s="305"/>
+      <c r="K1" s="305"/>
+      <c r="L1" s="306"/>
     </row>
     <row r="2" spans="2:19" ht="16.2" thickBot="1">
       <c r="B2" s="132"/>
@@ -26868,17 +28515,17 @@
       </c>
     </row>
     <row r="2" spans="2:15" ht="15" thickBot="1">
-      <c r="C2" s="300" t="s">
+      <c r="C2" s="307" t="s">
         <v>130</v>
       </c>
-      <c r="D2" s="301"/>
-      <c r="E2" s="301"/>
-      <c r="F2" s="301"/>
-      <c r="G2" s="301"/>
-      <c r="H2" s="301"/>
-      <c r="I2" s="301"/>
-      <c r="J2" s="301"/>
-      <c r="K2" s="302"/>
+      <c r="D2" s="308"/>
+      <c r="E2" s="308"/>
+      <c r="F2" s="308"/>
+      <c r="G2" s="308"/>
+      <c r="H2" s="308"/>
+      <c r="I2" s="308"/>
+      <c r="J2" s="308"/>
+      <c r="K2" s="309"/>
       <c r="O2" s="1" t="s">
         <v>203</v>
       </c>
@@ -27502,10 +29149,10 @@
       </c>
     </row>
     <row r="17" spans="3:12" ht="15" thickBot="1">
-      <c r="C17" s="303" t="s">
+      <c r="C17" s="310" t="s">
         <v>137</v>
       </c>
-      <c r="D17" s="304"/>
+      <c r="D17" s="311"/>
       <c r="E17" s="205">
         <f>E16-E15</f>
         <v>0.2</v>
@@ -27543,31 +29190,31 @@
       <c r="C18" s="42" t="s">
         <v>133</v>
       </c>
-      <c r="D18" s="305" t="s">
+      <c r="D18" s="312" t="s">
         <v>138</v>
       </c>
-      <c r="E18" s="306"/>
-      <c r="F18" s="306"/>
-      <c r="G18" s="306"/>
-      <c r="H18" s="306"/>
-      <c r="I18" s="306"/>
-      <c r="J18" s="306"/>
-      <c r="K18" s="307"/>
+      <c r="E18" s="313"/>
+      <c r="F18" s="313"/>
+      <c r="G18" s="313"/>
+      <c r="H18" s="313"/>
+      <c r="I18" s="313"/>
+      <c r="J18" s="313"/>
+      <c r="K18" s="314"/>
     </row>
     <row r="19" spans="3:12" ht="15" thickBot="1">
       <c r="C19" s="57" t="s">
         <v>135</v>
       </c>
-      <c r="D19" s="308" t="s">
+      <c r="D19" s="315" t="s">
         <v>139</v>
       </c>
-      <c r="E19" s="309"/>
-      <c r="F19" s="309"/>
-      <c r="G19" s="309"/>
-      <c r="H19" s="309"/>
-      <c r="I19" s="309"/>
-      <c r="J19" s="309"/>
-      <c r="K19" s="310"/>
+      <c r="E19" s="316"/>
+      <c r="F19" s="316"/>
+      <c r="G19" s="316"/>
+      <c r="H19" s="316"/>
+      <c r="I19" s="316"/>
+      <c r="J19" s="316"/>
+      <c r="K19" s="317"/>
     </row>
     <row r="21" spans="3:12">
       <c r="D21" s="1" t="s">
@@ -28526,35 +30173,35 @@
       </c>
     </row>
     <row r="30" spans="1:15" ht="14.4" customHeight="1">
-      <c r="B30" s="288" t="s">
+      <c r="B30" s="295" t="s">
         <v>220</v>
       </c>
-      <c r="C30" s="288"/>
-      <c r="D30" s="288"/>
-      <c r="E30" s="288"/>
-      <c r="F30" s="288"/>
-      <c r="G30" s="288"/>
-      <c r="H30" s="288"/>
-      <c r="I30" s="288"/>
-      <c r="J30" s="288"/>
-      <c r="K30" s="288"/>
-      <c r="L30" s="288"/>
+      <c r="C30" s="295"/>
+      <c r="D30" s="295"/>
+      <c r="E30" s="295"/>
+      <c r="F30" s="295"/>
+      <c r="G30" s="295"/>
+      <c r="H30" s="295"/>
+      <c r="I30" s="295"/>
+      <c r="J30" s="295"/>
+      <c r="K30" s="295"/>
+      <c r="L30" s="295"/>
       <c r="M30" s="285"/>
       <c r="N30" s="285"/>
       <c r="O30" s="285"/>
     </row>
     <row r="31" spans="1:15">
-      <c r="B31" s="288"/>
-      <c r="C31" s="288"/>
-      <c r="D31" s="288"/>
-      <c r="E31" s="288"/>
-      <c r="F31" s="288"/>
-      <c r="G31" s="288"/>
-      <c r="H31" s="288"/>
-      <c r="I31" s="288"/>
-      <c r="J31" s="288"/>
-      <c r="K31" s="288"/>
-      <c r="L31" s="288"/>
+      <c r="B31" s="295"/>
+      <c r="C31" s="295"/>
+      <c r="D31" s="295"/>
+      <c r="E31" s="295"/>
+      <c r="F31" s="295"/>
+      <c r="G31" s="295"/>
+      <c r="H31" s="295"/>
+      <c r="I31" s="295"/>
+      <c r="J31" s="295"/>
+      <c r="K31" s="295"/>
+      <c r="L31" s="295"/>
       <c r="M31" s="285"/>
       <c r="N31" s="285"/>
       <c r="O31" s="285"/>
@@ -28565,72 +30212,72 @@
       </c>
     </row>
     <row r="34" spans="2:12">
-      <c r="B34" s="290" t="s">
+      <c r="B34" s="297" t="s">
         <v>222</v>
       </c>
-      <c r="C34" s="290"/>
-      <c r="D34" s="290"/>
-      <c r="E34" s="290"/>
-      <c r="F34" s="290"/>
-      <c r="G34" s="290"/>
-      <c r="H34" s="290"/>
-      <c r="I34" s="290"/>
-      <c r="J34" s="290"/>
-      <c r="K34" s="290"/>
+      <c r="C34" s="297"/>
+      <c r="D34" s="297"/>
+      <c r="E34" s="297"/>
+      <c r="F34" s="297"/>
+      <c r="G34" s="297"/>
+      <c r="H34" s="297"/>
+      <c r="I34" s="297"/>
+      <c r="J34" s="297"/>
+      <c r="K34" s="297"/>
     </row>
     <row r="36" spans="2:12">
-      <c r="B36" s="289" t="s">
+      <c r="B36" s="296" t="s">
         <v>223</v>
       </c>
-      <c r="C36" s="289"/>
-      <c r="D36" s="289"/>
-      <c r="E36" s="289"/>
-      <c r="F36" s="289"/>
-      <c r="G36" s="289"/>
-      <c r="H36" s="289"/>
-      <c r="I36" s="289"/>
-      <c r="J36" s="289"/>
-      <c r="K36" s="289"/>
-      <c r="L36" s="289"/>
+      <c r="C36" s="296"/>
+      <c r="D36" s="296"/>
+      <c r="E36" s="296"/>
+      <c r="F36" s="296"/>
+      <c r="G36" s="296"/>
+      <c r="H36" s="296"/>
+      <c r="I36" s="296"/>
+      <c r="J36" s="296"/>
+      <c r="K36" s="296"/>
+      <c r="L36" s="296"/>
     </row>
     <row r="37" spans="2:12">
-      <c r="B37" s="289"/>
-      <c r="C37" s="289"/>
-      <c r="D37" s="289"/>
-      <c r="E37" s="289"/>
-      <c r="F37" s="289"/>
-      <c r="G37" s="289"/>
-      <c r="H37" s="289"/>
-      <c r="I37" s="289"/>
-      <c r="J37" s="289"/>
-      <c r="K37" s="289"/>
-      <c r="L37" s="289"/>
+      <c r="B37" s="296"/>
+      <c r="C37" s="296"/>
+      <c r="D37" s="296"/>
+      <c r="E37" s="296"/>
+      <c r="F37" s="296"/>
+      <c r="G37" s="296"/>
+      <c r="H37" s="296"/>
+      <c r="I37" s="296"/>
+      <c r="J37" s="296"/>
+      <c r="K37" s="296"/>
+      <c r="L37" s="296"/>
     </row>
     <row r="39" spans="2:12">
-      <c r="B39" s="289" t="s">
+      <c r="B39" s="296" t="s">
         <v>224</v>
       </c>
-      <c r="C39" s="289"/>
-      <c r="D39" s="289"/>
-      <c r="E39" s="289"/>
-      <c r="F39" s="289"/>
-      <c r="G39" s="289"/>
-      <c r="H39" s="289"/>
-      <c r="I39" s="289"/>
-      <c r="J39" s="289"/>
-      <c r="K39" s="289"/>
+      <c r="C39" s="296"/>
+      <c r="D39" s="296"/>
+      <c r="E39" s="296"/>
+      <c r="F39" s="296"/>
+      <c r="G39" s="296"/>
+      <c r="H39" s="296"/>
+      <c r="I39" s="296"/>
+      <c r="J39" s="296"/>
+      <c r="K39" s="296"/>
     </row>
     <row r="40" spans="2:12">
-      <c r="B40" s="289"/>
-      <c r="C40" s="289"/>
-      <c r="D40" s="289"/>
-      <c r="E40" s="289"/>
-      <c r="F40" s="289"/>
-      <c r="G40" s="289"/>
-      <c r="H40" s="289"/>
-      <c r="I40" s="289"/>
-      <c r="J40" s="289"/>
-      <c r="K40" s="289"/>
+      <c r="B40" s="296"/>
+      <c r="C40" s="296"/>
+      <c r="D40" s="296"/>
+      <c r="E40" s="296"/>
+      <c r="F40" s="296"/>
+      <c r="G40" s="296"/>
+      <c r="H40" s="296"/>
+      <c r="I40" s="296"/>
+      <c r="J40" s="296"/>
+      <c r="K40" s="296"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -29923,10 +31570,10 @@
         <f t="shared" ref="G4:G7" si="1">(E4-F4)^2</f>
         <v>201.88227631617858</v>
       </c>
-      <c r="I4" s="314" t="s">
+      <c r="I4" s="290" t="s">
         <v>158</v>
       </c>
-      <c r="J4" s="314"/>
+      <c r="J4" s="290"/>
       <c r="K4"/>
       <c r="L4"/>
       <c r="M4"/>
@@ -29956,10 +31603,10 @@
         <f t="shared" si="1"/>
         <v>3.6803544890932072</v>
       </c>
-      <c r="I5" s="311" t="s">
+      <c r="I5" t="s">
         <v>160</v>
       </c>
-      <c r="J5" s="311">
+      <c r="J5">
         <v>0.98928820282730667</v>
       </c>
       <c r="K5"/>
@@ -29991,10 +31638,10 @@
         <f t="shared" si="1"/>
         <v>98.215851772980997</v>
       </c>
-      <c r="I6" s="311" t="s">
+      <c r="I6" t="s">
         <v>162</v>
       </c>
-      <c r="J6" s="311">
+      <c r="J6">
         <v>0.97869114825328229</v>
       </c>
       <c r="K6"/>
@@ -30026,10 +31673,10 @@
         <f t="shared" si="1"/>
         <v>59.960938396634141</v>
       </c>
-      <c r="I7" s="311" t="s">
+      <c r="I7" t="s">
         <v>164</v>
       </c>
-      <c r="J7" s="311">
+      <c r="J7">
         <v>0.95738229650656459</v>
       </c>
       <c r="K7"/>
@@ -30045,10 +31692,10 @@
         <f>SUM(G3:G7)</f>
         <v>392.50904917453994</v>
       </c>
-      <c r="I8" s="311" t="s">
+      <c r="I8" t="s">
         <v>165</v>
       </c>
-      <c r="J8" s="311">
+      <c r="J8">
         <v>14.009087214635695</v>
       </c>
       <c r="K8"/>
@@ -30060,10 +31707,10 @@
       <c r="Q8"/>
     </row>
     <row r="9" spans="2:17" ht="15" thickBot="1">
-      <c r="I9" s="312" t="s">
+      <c r="I9" s="288" t="s">
         <v>166</v>
       </c>
-      <c r="J9" s="312">
+      <c r="J9" s="288">
         <v>5</v>
       </c>
       <c r="K9"/>
@@ -30129,20 +31776,20 @@
         <v>560.91153880109482</v>
       </c>
       <c r="G12" s="240"/>
-      <c r="I12" s="313"/>
-      <c r="J12" s="313" t="s">
+      <c r="I12" s="289"/>
+      <c r="J12" s="289" t="s">
         <v>168</v>
       </c>
-      <c r="K12" s="313" t="s">
+      <c r="K12" s="289" t="s">
         <v>169</v>
       </c>
-      <c r="L12" s="313" t="s">
+      <c r="L12" s="289" t="s">
         <v>170</v>
       </c>
-      <c r="M12" s="313" t="s">
+      <c r="M12" s="289" t="s">
         <v>171</v>
       </c>
-      <c r="N12" s="313" t="s">
+      <c r="N12" s="289" t="s">
         <v>172</v>
       </c>
       <c r="O12"/>
@@ -30150,22 +31797,22 @@
       <c r="Q12"/>
     </row>
     <row r="13" spans="2:17" ht="14.4">
-      <c r="I13" s="311" t="s">
+      <c r="I13" t="s">
         <v>173</v>
       </c>
-      <c r="J13" s="311">
+      <c r="J13">
         <v>2</v>
       </c>
-      <c r="K13" s="311">
+      <c r="K13">
         <v>18027.49095082546</v>
       </c>
-      <c r="L13" s="311">
+      <c r="L13">
         <v>9013.7454754127302</v>
       </c>
-      <c r="M13" s="311">
+      <c r="M13">
         <v>45.928854350588743</v>
       </c>
-      <c r="N13" s="311">
+      <c r="N13">
         <v>2.1308851746717622E-2</v>
       </c>
       <c r="O13"/>
@@ -30173,37 +31820,37 @@
       <c r="Q13"/>
     </row>
     <row r="14" spans="2:17" ht="14.4">
-      <c r="I14" s="311" t="s">
+      <c r="I14" t="s">
         <v>174</v>
       </c>
-      <c r="J14" s="311">
+      <c r="J14">
         <v>2</v>
       </c>
-      <c r="K14" s="318">
+      <c r="K14" s="294">
         <v>392.50904917453863</v>
       </c>
-      <c r="L14" s="311">
+      <c r="L14">
         <v>196.25452458726932</v>
       </c>
-      <c r="M14" s="311"/>
-      <c r="N14" s="311"/>
+      <c r="M14"/>
+      <c r="N14"/>
       <c r="O14"/>
       <c r="P14"/>
       <c r="Q14"/>
     </row>
     <row r="15" spans="2:17" ht="15" thickBot="1">
-      <c r="I15" s="312" t="s">
+      <c r="I15" s="288" t="s">
         <v>59</v>
       </c>
-      <c r="J15" s="312">
+      <c r="J15" s="288">
         <v>4</v>
       </c>
-      <c r="K15" s="312">
+      <c r="K15" s="288">
         <v>18420</v>
       </c>
-      <c r="L15" s="312"/>
-      <c r="M15" s="312"/>
-      <c r="N15" s="312"/>
+      <c r="L15" s="288"/>
+      <c r="M15" s="288"/>
+      <c r="N15" s="288"/>
       <c r="O15"/>
       <c r="P15"/>
       <c r="Q15"/>
@@ -30220,116 +31867,116 @@
       <c r="Q16"/>
     </row>
     <row r="17" spans="9:17" ht="14.4">
-      <c r="I17" s="313"/>
-      <c r="J17" s="313" t="s">
+      <c r="I17" s="289"/>
+      <c r="J17" s="289" t="s">
         <v>175</v>
       </c>
-      <c r="K17" s="313" t="s">
+      <c r="K17" s="289" t="s">
         <v>165</v>
       </c>
-      <c r="L17" s="313" t="s">
+      <c r="L17" s="289" t="s">
         <v>176</v>
       </c>
-      <c r="M17" s="313" t="s">
+      <c r="M17" s="289" t="s">
         <v>177</v>
       </c>
-      <c r="N17" s="313" t="s">
+      <c r="N17" s="289" t="s">
         <v>178</v>
       </c>
-      <c r="O17" s="313" t="s">
+      <c r="O17" s="289" t="s">
         <v>179</v>
       </c>
-      <c r="P17" s="313" t="s">
+      <c r="P17" s="289" t="s">
         <v>180</v>
       </c>
-      <c r="Q17" s="313" t="s">
+      <c r="Q17" s="289" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="18" spans="9:17" ht="14.4">
-      <c r="I18" s="311" t="s">
+      <c r="I18" t="s">
         <v>182</v>
       </c>
-      <c r="J18" s="315">
+      <c r="J18" s="291">
         <v>-44.81018804626126</v>
       </c>
-      <c r="K18" s="311">
+      <c r="K18">
         <v>69.246866630890381</v>
       </c>
-      <c r="L18" s="311">
+      <c r="L18">
         <v>-0.64710780756499753</v>
       </c>
-      <c r="M18" s="311">
+      <c r="M18">
         <v>0.58391574508017841</v>
       </c>
-      <c r="N18" s="311">
+      <c r="N18">
         <v>-342.75540778225883</v>
       </c>
-      <c r="O18" s="311">
+      <c r="O18">
         <v>253.13503168973631</v>
       </c>
-      <c r="P18" s="311">
+      <c r="P18">
         <v>-342.75540778225883</v>
       </c>
-      <c r="Q18" s="311">
+      <c r="Q18">
         <v>253.13503168973631</v>
       </c>
     </row>
     <row r="19" spans="9:17" ht="14.4">
-      <c r="I19" s="311" t="s">
+      <c r="I19" t="s">
         <v>152</v>
       </c>
-      <c r="J19" s="316">
+      <c r="J19" s="292">
         <v>87.640151849563026</v>
       </c>
-      <c r="K19" s="311">
+      <c r="K19">
         <v>15.237186664924886</v>
       </c>
-      <c r="L19" s="311">
+      <c r="L19">
         <v>5.7517279125618073</v>
       </c>
-      <c r="M19" s="311">
+      <c r="M19">
         <v>2.8922600815111749E-2</v>
       </c>
-      <c r="N19" s="311">
+      <c r="N19">
         <v>22.079829052021836</v>
       </c>
-      <c r="O19" s="311">
+      <c r="O19">
         <v>153.20047464710422</v>
       </c>
-      <c r="P19" s="311">
+      <c r="P19">
         <v>22.079829052021836</v>
       </c>
-      <c r="Q19" s="311">
+      <c r="Q19">
         <v>153.20047464710422</v>
       </c>
     </row>
     <row r="20" spans="9:17" ht="15" thickBot="1">
-      <c r="I20" s="312" t="s">
+      <c r="I20" s="288" t="s">
         <v>153</v>
       </c>
-      <c r="J20" s="317">
+      <c r="J20" s="293">
         <v>14.532974309172776</v>
       </c>
-      <c r="K20" s="312">
+      <c r="K20" s="288">
         <v>2.9137375361504319</v>
       </c>
-      <c r="L20" s="312">
+      <c r="L20" s="288">
         <v>4.9877431061870565</v>
       </c>
-      <c r="M20" s="312">
+      <c r="M20" s="288">
         <v>3.7924876930238542E-2</v>
       </c>
-      <c r="N20" s="312">
+      <c r="N20" s="288">
         <v>1.9961735454816427</v>
       </c>
-      <c r="O20" s="312">
+      <c r="O20" s="288">
         <v>27.069775072863909</v>
       </c>
-      <c r="P20" s="312">
+      <c r="P20" s="288">
         <v>1.9961735454816427</v>
       </c>
-      <c r="Q20" s="312">
+      <c r="Q20" s="288">
         <v>27.069775072863909</v>
       </c>
     </row>
@@ -32285,10 +33932,10 @@
       </c>
     </row>
     <row r="61" spans="2:22">
-      <c r="H61" s="291" t="s">
+      <c r="H61" s="298" t="s">
         <v>63</v>
       </c>
-      <c r="I61" s="291"/>
+      <c r="I61" s="298"/>
       <c r="T61" s="1" t="s">
         <v>64</v>
       </c>
@@ -32426,11 +34073,11 @@
       <c r="H1" s="67" t="s">
         <v>74</v>
       </c>
-      <c r="J1" s="292" t="s">
+      <c r="J1" s="299" t="s">
         <v>76</v>
       </c>
-      <c r="K1" s="292"/>
-      <c r="L1" s="292"/>
+      <c r="K1" s="299"/>
+      <c r="L1" s="299"/>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="251">
